--- a/research/traditional_assets/database/data/colombia/colombia_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_engineering_construction.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09917985134933119</v>
+        <v>0.09886197186960853</v>
       </c>
       <c r="C2">
-        <v>264.5040846454233</v>
+        <v>262.8228868424775</v>
       </c>
       <c r="D2">
-        <v>239.5040846454233</v>
+        <v>240.9388868424775</v>
       </c>
       <c r="E2">
-        <v>-186.5</v>
+        <v>-183.384</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.116</v>
       </c>
       <c r="G2">
         <v>25</v>
@@ -1445,28 +1445,28 @@
         <v>12.35</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1567348</v>
       </c>
       <c r="N2">
-        <v>12.35</v>
+        <v>12.1932652</v>
       </c>
       <c r="O2">
-        <v>4.3225</v>
+        <v>4.267642819999999</v>
       </c>
       <c r="P2">
-        <v>8.0275</v>
+        <v>7.92562238</v>
       </c>
       <c r="Q2">
-        <v>13.8775</v>
+        <v>13.77562238</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09917985134933119</v>
+        <v>0.09953032512081669</v>
       </c>
       <c r="T2">
-        <v>0.776741878503467</v>
+        <v>0.7818416989178838</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>78.79551956553362</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09886197186960853</v>
+        <v>0.09854409238988586</v>
       </c>
       <c r="C3">
-        <v>262.8228868424775</v>
+        <v>261.1589836465762</v>
       </c>
       <c r="D3">
-        <v>240.9388868424775</v>
+        <v>242.3909836465763</v>
       </c>
       <c r="E3">
-        <v>-183.384</v>
+        <v>-180.268</v>
       </c>
       <c r="F3">
-        <v>3.116</v>
+        <v>6.232</v>
       </c>
       <c r="G3">
         <v>25</v>
@@ -1527,28 +1527,28 @@
         <v>12.35</v>
       </c>
       <c r="M3">
-        <v>0.1567348</v>
+        <v>0.3134696</v>
       </c>
       <c r="N3">
-        <v>12.1932652</v>
+        <v>12.0365304</v>
       </c>
       <c r="O3">
-        <v>4.267642819999999</v>
+        <v>4.21278564</v>
       </c>
       <c r="P3">
-        <v>7.92562238</v>
+        <v>7.82374476</v>
       </c>
       <c r="Q3">
-        <v>13.77562238</v>
+        <v>13.67374476</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09953032512081669</v>
+        <v>0.09988795141825088</v>
       </c>
       <c r="T3">
-        <v>0.7818416989178838</v>
+        <v>0.7870455972999416</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>78.79551956553362</v>
+        <v>39.39775978276681</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09854409238988586</v>
+        <v>0.0982262129101632</v>
       </c>
       <c r="C4">
-        <v>261.1589836465762</v>
+        <v>259.5126896484779</v>
       </c>
       <c r="D4">
-        <v>242.3909836465763</v>
+        <v>243.8606896484779</v>
       </c>
       <c r="E4">
-        <v>-180.268</v>
+        <v>-177.152</v>
       </c>
       <c r="F4">
-        <v>6.232</v>
+        <v>9.348000000000001</v>
       </c>
       <c r="G4">
         <v>25</v>
@@ -1609,28 +1609,28 @@
         <v>12.35</v>
       </c>
       <c r="M4">
-        <v>0.3134696</v>
+        <v>0.4702044</v>
       </c>
       <c r="N4">
-        <v>12.0365304</v>
+        <v>11.8797956</v>
       </c>
       <c r="O4">
-        <v>4.21278564</v>
+        <v>4.15792846</v>
       </c>
       <c r="P4">
-        <v>7.82374476</v>
+        <v>7.72186714</v>
       </c>
       <c r="Q4">
-        <v>13.67374476</v>
+        <v>13.57186714</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09988795141825088</v>
+        <v>0.1002529514537765</v>
       </c>
       <c r="T4">
-        <v>0.7870455972999416</v>
+        <v>0.7923567925558562</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.39775978276681</v>
+        <v>26.26517318851121</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0982262129101632</v>
+        <v>0.09790833343044056</v>
       </c>
       <c r="C5">
-        <v>259.5126896484779</v>
+        <v>257.8843271154052</v>
       </c>
       <c r="D5">
-        <v>243.8606896484779</v>
+        <v>245.3483271154052</v>
       </c>
       <c r="E5">
-        <v>-177.152</v>
+        <v>-174.036</v>
       </c>
       <c r="F5">
-        <v>9.348000000000001</v>
+        <v>12.464</v>
       </c>
       <c r="G5">
         <v>25</v>
@@ -1691,28 +1691,28 @@
         <v>12.35</v>
       </c>
       <c r="M5">
-        <v>0.4702044</v>
+        <v>0.6269392</v>
       </c>
       <c r="N5">
-        <v>11.8797956</v>
+        <v>11.7230608</v>
       </c>
       <c r="O5">
-        <v>4.15792846</v>
+        <v>4.103071279999999</v>
       </c>
       <c r="P5">
-        <v>7.72186714</v>
+        <v>7.61998952</v>
       </c>
       <c r="Q5">
-        <v>13.57186714</v>
+        <v>13.46998952</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1002529514537765</v>
+        <v>0.1006255556567089</v>
       </c>
       <c r="T5">
-        <v>0.7923567925558562</v>
+        <v>0.7977786377129359</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.26517318851121</v>
+        <v>19.69887989138341</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09790833343044056</v>
+        <v>0.09759045395071789</v>
       </c>
       <c r="C6">
-        <v>257.8843271154052</v>
+        <v>256.2742262266292</v>
       </c>
       <c r="D6">
-        <v>245.3483271154052</v>
+        <v>246.8542262266292</v>
       </c>
       <c r="E6">
-        <v>-174.036</v>
+        <v>-170.92</v>
       </c>
       <c r="F6">
-        <v>12.464</v>
+        <v>15.58</v>
       </c>
       <c r="G6">
         <v>25</v>
@@ -1773,28 +1773,28 @@
         <v>12.35</v>
       </c>
       <c r="M6">
-        <v>0.6269392</v>
+        <v>0.7836740000000001</v>
       </c>
       <c r="N6">
-        <v>11.7230608</v>
+        <v>11.566326</v>
       </c>
       <c r="O6">
-        <v>4.103071279999999</v>
+        <v>4.0482141</v>
       </c>
       <c r="P6">
-        <v>7.61998952</v>
+        <v>7.5181119</v>
       </c>
       <c r="Q6">
-        <v>13.46998952</v>
+        <v>13.3681119</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1006255556567089</v>
+        <v>0.1010060041586504</v>
       </c>
       <c r="T6">
-        <v>0.7977786377129359</v>
+        <v>0.8033146269785856</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.69887989138341</v>
+        <v>15.75910391310672</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09759045395071789</v>
+        <v>0.09727257447099523</v>
       </c>
       <c r="C7">
-        <v>256.2742262266292</v>
+        <v>254.6827253177807</v>
       </c>
       <c r="D7">
-        <v>246.8542262266292</v>
+        <v>248.3787253177807</v>
       </c>
       <c r="E7">
-        <v>-170.92</v>
+        <v>-167.804</v>
       </c>
       <c r="F7">
-        <v>15.58</v>
+        <v>18.696</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -1855,28 +1855,28 @@
         <v>12.35</v>
       </c>
       <c r="M7">
-        <v>0.7836740000000001</v>
+        <v>0.9404088</v>
       </c>
       <c r="N7">
-        <v>11.566326</v>
+        <v>11.4095912</v>
       </c>
       <c r="O7">
-        <v>4.0482141</v>
+        <v>3.99335692</v>
       </c>
       <c r="P7">
-        <v>7.5181119</v>
+        <v>7.416234279999999</v>
       </c>
       <c r="Q7">
-        <v>13.3681119</v>
+        <v>13.26623428</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1010060041586504</v>
+        <v>0.1013945473095694</v>
       </c>
       <c r="T7">
-        <v>0.8033146269785856</v>
+        <v>0.8089684032498875</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.75910391310672</v>
+        <v>13.1325865942556</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09727257447099523</v>
+        <v>0.09702294499127256</v>
       </c>
       <c r="C8">
-        <v>254.6827253177807</v>
+        <v>252.7771721592463</v>
       </c>
       <c r="D8">
-        <v>248.3787253177807</v>
+        <v>249.5891721592463</v>
       </c>
       <c r="E8">
-        <v>-167.804</v>
+        <v>-164.688</v>
       </c>
       <c r="F8">
-        <v>18.696</v>
+        <v>21.812</v>
       </c>
       <c r="G8">
         <v>25</v>
@@ -1937,45 +1937,45 @@
         <v>12.35</v>
       </c>
       <c r="M8">
-        <v>0.9404088</v>
+        <v>1.1298616</v>
       </c>
       <c r="N8">
-        <v>11.4095912</v>
+        <v>11.2201384</v>
       </c>
       <c r="O8">
-        <v>3.99335692</v>
+        <v>3.92704844</v>
       </c>
       <c r="P8">
-        <v>7.416234279999999</v>
+        <v>7.29308996</v>
       </c>
       <c r="Q8">
-        <v>13.26623428</v>
+        <v>13.14308996</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1013945473095694</v>
+        <v>0.1017914462271748</v>
       </c>
       <c r="T8">
-        <v>0.8089684032498875</v>
+        <v>0.8147437661076687</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.1325865942556</v>
+        <v>10.93054228942731</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09702294499127255</v>
+        <v>0.09680321551154993</v>
       </c>
       <c r="C9">
-        <v>252.7771721592464</v>
+        <v>250.7364396378338</v>
       </c>
       <c r="D9">
-        <v>249.5891721592464</v>
+        <v>250.6644396378338</v>
       </c>
       <c r="E9">
-        <v>-164.688</v>
+        <v>-161.572</v>
       </c>
       <c r="F9">
-        <v>21.812</v>
+        <v>24.928</v>
       </c>
       <c r="G9">
         <v>25</v>
@@ -2019,45 +2019,45 @@
         <v>12.35</v>
       </c>
       <c r="M9">
-        <v>1.1298616</v>
+        <v>1.333648</v>
       </c>
       <c r="N9">
-        <v>11.2201384</v>
+        <v>11.016352</v>
       </c>
       <c r="O9">
-        <v>3.92704844</v>
+        <v>3.855723199999999</v>
       </c>
       <c r="P9">
-        <v>7.29308996</v>
+        <v>7.1606288</v>
       </c>
       <c r="Q9">
-        <v>13.14308996</v>
+        <v>13.0106288</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1017914462271748</v>
+        <v>0.1021969733821195</v>
       </c>
       <c r="T9">
-        <v>0.8147437661076687</v>
+        <v>0.8206446803319237</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.93054228942731</v>
+        <v>9.26031456576248</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09680321551154993</v>
+        <v>0.09650613603182726</v>
       </c>
       <c r="C10">
-        <v>250.7364396378338</v>
+        <v>249.0890441725165</v>
       </c>
       <c r="D10">
-        <v>250.6644396378338</v>
+        <v>252.1330441725165</v>
       </c>
       <c r="E10">
-        <v>-161.572</v>
+        <v>-158.456</v>
       </c>
       <c r="F10">
-        <v>24.928</v>
+        <v>28.044</v>
       </c>
       <c r="G10">
         <v>25</v>
@@ -2101,28 +2101,28 @@
         <v>12.35</v>
       </c>
       <c r="M10">
-        <v>1.333648</v>
+        <v>1.500354</v>
       </c>
       <c r="N10">
-        <v>11.016352</v>
+        <v>10.849646</v>
       </c>
       <c r="O10">
-        <v>3.855723199999999</v>
+        <v>3.7973761</v>
       </c>
       <c r="P10">
-        <v>7.1606288</v>
+        <v>7.052269900000001</v>
       </c>
       <c r="Q10">
-        <v>13.0106288</v>
+        <v>12.9022699</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1021969733821195</v>
+        <v>0.1026114132217882</v>
       </c>
       <c r="T10">
-        <v>0.8206446803319237</v>
+        <v>0.8266752849786898</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.26031456576248</v>
+        <v>8.231390725122203</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09650613603182726</v>
+        <v>0.0962610565521046</v>
       </c>
       <c r="C11">
-        <v>249.0890441725165</v>
+        <v>247.1976050420038</v>
       </c>
       <c r="D11">
-        <v>252.1330441725165</v>
+        <v>253.3576050420038</v>
       </c>
       <c r="E11">
-        <v>-158.456</v>
+        <v>-155.34</v>
       </c>
       <c r="F11">
-        <v>28.044</v>
+        <v>31.16</v>
       </c>
       <c r="G11">
         <v>25</v>
@@ -2183,45 +2183,45 @@
         <v>12.35</v>
       </c>
       <c r="M11">
-        <v>1.500354</v>
+        <v>1.691988</v>
       </c>
       <c r="N11">
-        <v>10.849646</v>
+        <v>10.658012</v>
       </c>
       <c r="O11">
-        <v>3.7973761</v>
+        <v>3.7303042</v>
       </c>
       <c r="P11">
-        <v>7.052269900000001</v>
+        <v>6.9277078</v>
       </c>
       <c r="Q11">
-        <v>12.9022699</v>
+        <v>12.7777078</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1026114132217882</v>
+        <v>0.1030350628356718</v>
       </c>
       <c r="T11">
-        <v>0.8266752849786898</v>
+        <v>0.8328399030620507</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.231390725122203</v>
+        <v>7.299106140232673</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0962610565521046</v>
+        <v>0.09596917707238194</v>
       </c>
       <c r="C12">
-        <v>247.1976050420038</v>
+        <v>245.5556153857801</v>
       </c>
       <c r="D12">
-        <v>253.3576050420038</v>
+        <v>254.8316153857801</v>
       </c>
       <c r="E12">
-        <v>-155.34</v>
+        <v>-152.224</v>
       </c>
       <c r="F12">
-        <v>31.16</v>
+        <v>34.276</v>
       </c>
       <c r="G12">
         <v>25</v>
@@ -2265,28 +2265,28 @@
         <v>12.35</v>
       </c>
       <c r="M12">
-        <v>1.691988</v>
+        <v>1.8611868</v>
       </c>
       <c r="N12">
-        <v>10.658012</v>
+        <v>10.4888132</v>
       </c>
       <c r="O12">
-        <v>3.7303042</v>
+        <v>3.671084619999999</v>
       </c>
       <c r="P12">
-        <v>6.9277078</v>
+        <v>6.81772858</v>
       </c>
       <c r="Q12">
-        <v>12.7777078</v>
+        <v>12.66772858</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1030350628356718</v>
+        <v>0.1034682326655977</v>
       </c>
       <c r="T12">
-        <v>0.8328399030620507</v>
+        <v>0.839143051888858</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.299106140232672</v>
+        <v>6.635551036575156</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09596917707238194</v>
+        <v>0.09575529759265927</v>
       </c>
       <c r="C13">
-        <v>245.5556153857801</v>
+        <v>243.5306558948373</v>
       </c>
       <c r="D13">
-        <v>254.8316153857801</v>
+        <v>255.9226558948373</v>
       </c>
       <c r="E13">
-        <v>-152.224</v>
+        <v>-149.108</v>
       </c>
       <c r="F13">
-        <v>34.276</v>
+        <v>37.392</v>
       </c>
       <c r="G13">
         <v>25</v>
@@ -2347,45 +2347,45 @@
         <v>12.35</v>
       </c>
       <c r="M13">
-        <v>1.8611868</v>
+        <v>2.0677776</v>
       </c>
       <c r="N13">
-        <v>10.4888132</v>
+        <v>10.2822224</v>
       </c>
       <c r="O13">
-        <v>3.671084619999999</v>
+        <v>3.598777839999999</v>
       </c>
       <c r="P13">
-        <v>6.81772858</v>
+        <v>6.68344456</v>
       </c>
       <c r="Q13">
-        <v>12.66772858</v>
+        <v>12.53344456</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1034682326655977</v>
+        <v>0.1039112472643855</v>
       </c>
       <c r="T13">
-        <v>0.839143051888858</v>
+        <v>0.8455894540980925</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.635551036575156</v>
+        <v>5.972595892324202</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09575529759265927</v>
+        <v>0.09546991811293662</v>
       </c>
       <c r="C14">
-        <v>243.5306558948373</v>
+        <v>241.8850644874676</v>
       </c>
       <c r="D14">
-        <v>255.9226558948373</v>
+        <v>257.3930644874677</v>
       </c>
       <c r="E14">
-        <v>-149.108</v>
+        <v>-145.992</v>
       </c>
       <c r="F14">
-        <v>37.392</v>
+        <v>40.508</v>
       </c>
       <c r="G14">
         <v>25</v>
@@ -2429,28 +2429,28 @@
         <v>12.35</v>
       </c>
       <c r="M14">
-        <v>2.0677776</v>
+        <v>2.2400924</v>
       </c>
       <c r="N14">
-        <v>10.2822224</v>
+        <v>10.1099076</v>
       </c>
       <c r="O14">
-        <v>3.598777839999999</v>
+        <v>3.53846766</v>
       </c>
       <c r="P14">
-        <v>6.68344456</v>
+        <v>6.571439939999999</v>
       </c>
       <c r="Q14">
-        <v>12.53344456</v>
+        <v>12.42143994</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1039112472643855</v>
+        <v>0.1043644461068237</v>
       </c>
       <c r="T14">
-        <v>0.8455894540980925</v>
+        <v>0.8521840494615623</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.972595892324202</v>
+        <v>5.513165439068494</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09546991811293662</v>
+        <v>0.09518453863321395</v>
       </c>
       <c r="C15">
-        <v>241.8850644874676</v>
+        <v>240.2564672426744</v>
       </c>
       <c r="D15">
-        <v>257.3930644874677</v>
+        <v>258.8804672426744</v>
       </c>
       <c r="E15">
-        <v>-145.992</v>
+        <v>-142.876</v>
       </c>
       <c r="F15">
-        <v>40.508</v>
+        <v>43.62400000000001</v>
       </c>
       <c r="G15">
         <v>25</v>
@@ -2511,28 +2511,28 @@
         <v>12.35</v>
       </c>
       <c r="M15">
-        <v>2.2400924</v>
+        <v>2.412407200000001</v>
       </c>
       <c r="N15">
-        <v>10.1099076</v>
+        <v>9.937592799999999</v>
       </c>
       <c r="O15">
-        <v>3.53846766</v>
+        <v>3.47815748</v>
       </c>
       <c r="P15">
-        <v>6.571439939999999</v>
+        <v>6.459435319999999</v>
       </c>
       <c r="Q15">
-        <v>12.42143994</v>
+        <v>12.30943532</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1043644461068237</v>
+        <v>0.1048281844572255</v>
       </c>
       <c r="T15">
-        <v>0.8521840494615623</v>
+        <v>0.8589320075079037</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.513165439068494</v>
+        <v>5.119367907706459</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09518453863321395</v>
+        <v>0.0948991591534913</v>
       </c>
       <c r="C16">
-        <v>240.2564672426744</v>
+        <v>238.6451604864245</v>
       </c>
       <c r="D16">
-        <v>258.8804672426744</v>
+        <v>260.3851604864245</v>
       </c>
       <c r="E16">
-        <v>-142.876</v>
+        <v>-139.76</v>
       </c>
       <c r="F16">
-        <v>43.62400000000001</v>
+        <v>46.74000000000001</v>
       </c>
       <c r="G16">
         <v>25</v>
@@ -2593,28 +2593,28 @@
         <v>12.35</v>
       </c>
       <c r="M16">
-        <v>2.412407200000001</v>
+        <v>2.584722000000001</v>
       </c>
       <c r="N16">
-        <v>9.937592799999999</v>
+        <v>9.765277999999999</v>
       </c>
       <c r="O16">
-        <v>3.47815748</v>
+        <v>3.417847299999999</v>
       </c>
       <c r="P16">
-        <v>6.459435319999999</v>
+        <v>6.347430699999999</v>
       </c>
       <c r="Q16">
-        <v>12.30943532</v>
+        <v>12.1974307</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1048281844572255</v>
+        <v>0.1053028342982251</v>
       </c>
       <c r="T16">
-        <v>0.8589320075079037</v>
+        <v>0.8658387410376882</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.119367907706459</v>
+        <v>4.778076713859361</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0948991591534913</v>
+        <v>0.09487377967376864</v>
       </c>
       <c r="C17">
-        <v>238.6451604864245</v>
+        <v>235.6638238432024</v>
       </c>
       <c r="D17">
-        <v>260.3851604864245</v>
+        <v>260.5198238432024</v>
       </c>
       <c r="E17">
-        <v>-139.76</v>
+        <v>-136.644</v>
       </c>
       <c r="F17">
-        <v>46.74</v>
+        <v>49.856</v>
       </c>
       <c r="G17">
         <v>25</v>
@@ -2675,45 +2675,45 @@
         <v>12.35</v>
       </c>
       <c r="M17">
-        <v>2.584722</v>
+        <v>2.8816768</v>
       </c>
       <c r="N17">
-        <v>9.765277999999999</v>
+        <v>9.4683232</v>
       </c>
       <c r="O17">
-        <v>3.417847299999999</v>
+        <v>3.31391312</v>
       </c>
       <c r="P17">
-        <v>6.347430699999999</v>
+        <v>6.15441008</v>
       </c>
       <c r="Q17">
-        <v>12.1974307</v>
+        <v>12.00441008</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1053028342982251</v>
+        <v>0.105788785325915</v>
       </c>
       <c r="T17">
-        <v>0.8658387410376882</v>
+        <v>0.8729099206038963</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.778076713859361</v>
+        <v>4.285699215123639</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09487377967376864</v>
+        <v>0.09460465019404599</v>
       </c>
       <c r="C18">
-        <v>235.6638238432024</v>
+        <v>233.9844403207223</v>
       </c>
       <c r="D18">
-        <v>260.5198238432024</v>
+        <v>261.9564403207223</v>
       </c>
       <c r="E18">
-        <v>-136.644</v>
+        <v>-133.528</v>
       </c>
       <c r="F18">
-        <v>49.856</v>
+        <v>52.97200000000001</v>
       </c>
       <c r="G18">
         <v>25</v>
@@ -2757,28 +2757,28 @@
         <v>12.35</v>
       </c>
       <c r="M18">
-        <v>2.8816768</v>
+        <v>3.061781600000001</v>
       </c>
       <c r="N18">
-        <v>9.4683232</v>
+        <v>9.288218399999998</v>
       </c>
       <c r="O18">
-        <v>3.31391312</v>
+        <v>3.250876439999999</v>
       </c>
       <c r="P18">
-        <v>6.15441008</v>
+        <v>6.037341959999999</v>
       </c>
       <c r="Q18">
-        <v>12.00441008</v>
+        <v>11.88734196</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.105788785325915</v>
+        <v>0.1062864460169229</v>
       </c>
       <c r="T18">
-        <v>0.8729099206038963</v>
+        <v>0.8801514900391696</v>
       </c>
       <c r="U18">
         <v>0.0578</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.285699215123639</v>
+        <v>4.033599261292835</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09460465019404599</v>
+        <v>0.09474502071432331</v>
       </c>
       <c r="C19">
-        <v>233.9844403207223</v>
+        <v>230.1171695830422</v>
       </c>
       <c r="D19">
-        <v>261.9564403207223</v>
+        <v>261.2051695830422</v>
       </c>
       <c r="E19">
-        <v>-133.528</v>
+        <v>-130.412</v>
       </c>
       <c r="F19">
-        <v>52.97200000000001</v>
+        <v>56.08800000000001</v>
       </c>
       <c r="G19">
         <v>25</v>
@@ -2839,45 +2839,45 @@
         <v>12.35</v>
       </c>
       <c r="M19">
-        <v>3.061781600000001</v>
+        <v>3.4381944</v>
       </c>
       <c r="N19">
-        <v>9.288218399999998</v>
+        <v>8.911805599999999</v>
       </c>
       <c r="O19">
-        <v>3.250876439999999</v>
+        <v>3.119131959999999</v>
       </c>
       <c r="P19">
-        <v>6.037341959999999</v>
+        <v>5.79267364</v>
       </c>
       <c r="Q19">
-        <v>11.88734196</v>
+        <v>11.64267364</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1062864460169229</v>
+        <v>0.106796244773565</v>
       </c>
       <c r="T19">
-        <v>0.8801514900391696</v>
+        <v>0.8875696831192055</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.033599261292835</v>
+        <v>3.592001662267846</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09474502071432332</v>
+        <v>0.09484444123460067</v>
       </c>
       <c r="C20">
-        <v>230.1171695830422</v>
+        <v>226.4716670909073</v>
       </c>
       <c r="D20">
-        <v>261.2051695830422</v>
+        <v>260.6756670909073</v>
       </c>
       <c r="E20">
-        <v>-130.412</v>
+        <v>-127.296</v>
       </c>
       <c r="F20">
-        <v>56.088</v>
+        <v>59.20400000000001</v>
       </c>
       <c r="G20">
         <v>25</v>
@@ -2921,45 +2921,45 @@
         <v>12.35</v>
       </c>
       <c r="M20">
-        <v>3.4381944</v>
+        <v>3.794976400000001</v>
       </c>
       <c r="N20">
-        <v>8.911805599999999</v>
+        <v>8.555023599999998</v>
       </c>
       <c r="O20">
-        <v>3.119131959999999</v>
+        <v>2.994258259999999</v>
       </c>
       <c r="P20">
-        <v>5.79267364</v>
+        <v>5.56076534</v>
       </c>
       <c r="Q20">
-        <v>11.64267364</v>
+        <v>11.41076534</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.106796244773565</v>
+        <v>0.107318631153828</v>
       </c>
       <c r="T20">
-        <v>0.8875696831192055</v>
+        <v>0.8951710414604771</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.592001662267846</v>
+        <v>3.254302187491863</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09484444123460067</v>
+        <v>0.09461626175487801</v>
       </c>
       <c r="C21">
-        <v>226.4716670909073</v>
+        <v>224.5741306920702</v>
       </c>
       <c r="D21">
-        <v>260.6756670909073</v>
+        <v>261.8941306920702</v>
       </c>
       <c r="E21">
-        <v>-127.296</v>
+        <v>-124.18</v>
       </c>
       <c r="F21">
-        <v>59.20400000000001</v>
+        <v>62.32000000000001</v>
       </c>
       <c r="G21">
         <v>25</v>
@@ -3003,28 +3003,28 @@
         <v>12.35</v>
       </c>
       <c r="M21">
-        <v>3.794976400000001</v>
+        <v>3.994712000000001</v>
       </c>
       <c r="N21">
-        <v>8.555023599999998</v>
+        <v>8.355287999999998</v>
       </c>
       <c r="O21">
-        <v>2.994258259999999</v>
+        <v>2.924350799999999</v>
       </c>
       <c r="P21">
-        <v>5.56076534</v>
+        <v>5.430937199999999</v>
       </c>
       <c r="Q21">
-        <v>11.41076534</v>
+        <v>11.2809372</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.107318631153828</v>
+        <v>0.1078540771935975</v>
       </c>
       <c r="T21">
-        <v>0.8951710414604771</v>
+        <v>0.9029624337602804</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.254302187491863</v>
+        <v>3.09158707811727</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09461626175487801</v>
+        <v>0.09545278227515534</v>
       </c>
       <c r="C22">
-        <v>224.5741306920702</v>
+        <v>217.0458942689417</v>
       </c>
       <c r="D22">
-        <v>261.8941306920702</v>
+        <v>257.4818942689417</v>
       </c>
       <c r="E22">
-        <v>-124.18</v>
+        <v>-121.064</v>
       </c>
       <c r="F22">
-        <v>62.32000000000001</v>
+        <v>65.43600000000001</v>
       </c>
       <c r="G22">
         <v>25</v>
@@ -3085,45 +3085,45 @@
         <v>12.35</v>
       </c>
       <c r="M22">
-        <v>3.994712000000001</v>
+        <v>4.704848400000001</v>
       </c>
       <c r="N22">
-        <v>8.355287999999998</v>
+        <v>7.645151599999998</v>
       </c>
       <c r="O22">
-        <v>2.924350799999999</v>
+        <v>2.675803059999999</v>
       </c>
       <c r="P22">
-        <v>5.430937199999999</v>
+        <v>4.969348539999999</v>
       </c>
       <c r="Q22">
-        <v>11.2809372</v>
+        <v>10.81934854</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1078540771935975</v>
+        <v>0.1084030788293106</v>
       </c>
       <c r="T22">
-        <v>0.9029624337602804</v>
+        <v>0.9109510764980534</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.09158707811727</v>
+        <v>2.624951741271833</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09545278227515534</v>
+        <v>0.09527530279543268</v>
       </c>
       <c r="C23">
-        <v>217.0458942689417</v>
+        <v>214.8535420295589</v>
       </c>
       <c r="D23">
-        <v>257.4818942689417</v>
+        <v>258.4055420295589</v>
       </c>
       <c r="E23">
-        <v>-121.064</v>
+        <v>-117.948</v>
       </c>
       <c r="F23">
-        <v>65.43600000000001</v>
+        <v>68.55200000000001</v>
       </c>
       <c r="G23">
         <v>25</v>
@@ -3167,28 +3167,28 @@
         <v>12.35</v>
       </c>
       <c r="M23">
-        <v>4.704848400000001</v>
+        <v>4.928888800000001</v>
       </c>
       <c r="N23">
-        <v>7.645151599999998</v>
+        <v>7.421111199999999</v>
       </c>
       <c r="O23">
-        <v>2.675803059999999</v>
+        <v>2.597388919999999</v>
       </c>
       <c r="P23">
-        <v>4.969348539999999</v>
+        <v>4.823722279999999</v>
       </c>
       <c r="Q23">
-        <v>10.81934854</v>
+        <v>10.67372228</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1084030788293106</v>
+        <v>0.1089661574300419</v>
       </c>
       <c r="T23">
-        <v>0.9109510764980534</v>
+        <v>0.9191445562291026</v>
       </c>
       <c r="U23">
         <v>0.07190000000000001</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.624951741271833</v>
+        <v>2.505635753032204</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09527530279543268</v>
+        <v>0.09568087331571004</v>
       </c>
       <c r="C24">
-        <v>214.8535420295589</v>
+        <v>209.6365028304222</v>
       </c>
       <c r="D24">
-        <v>258.4055420295589</v>
+        <v>256.3045028304222</v>
       </c>
       <c r="E24">
-        <v>-117.948</v>
+        <v>-114.832</v>
       </c>
       <c r="F24">
-        <v>68.55200000000001</v>
+        <v>71.66800000000001</v>
       </c>
       <c r="G24">
         <v>25</v>
@@ -3249,45 +3249,45 @@
         <v>12.35</v>
       </c>
       <c r="M24">
-        <v>4.928888800000001</v>
+        <v>5.432434400000001</v>
       </c>
       <c r="N24">
-        <v>7.421111199999999</v>
+        <v>6.917565599999999</v>
       </c>
       <c r="O24">
-        <v>2.597388919999999</v>
+        <v>2.421147959999999</v>
       </c>
       <c r="P24">
-        <v>4.823722279999999</v>
+        <v>4.496417639999999</v>
       </c>
       <c r="Q24">
-        <v>10.67372228</v>
+        <v>10.34641764</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1089661574300419</v>
+        <v>0.1095438614489741</v>
       </c>
       <c r="T24">
-        <v>0.9191445562291026</v>
+        <v>0.9275508536155038</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.505635753032204</v>
+        <v>2.273382261182942</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09568087331571004</v>
+        <v>0.09552874383598736</v>
       </c>
       <c r="C25">
-        <v>209.6365028304222</v>
+        <v>207.3045859915567</v>
       </c>
       <c r="D25">
-        <v>256.3045028304222</v>
+        <v>257.0885859915567</v>
       </c>
       <c r="E25">
-        <v>-114.832</v>
+        <v>-111.716</v>
       </c>
       <c r="F25">
-        <v>71.66800000000001</v>
+        <v>74.78400000000001</v>
       </c>
       <c r="G25">
         <v>25</v>
@@ -3331,28 +3331,28 @@
         <v>12.35</v>
       </c>
       <c r="M25">
-        <v>5.432434400000001</v>
+        <v>5.668627200000001</v>
       </c>
       <c r="N25">
-        <v>6.917565599999999</v>
+        <v>6.681372799999998</v>
       </c>
       <c r="O25">
-        <v>2.421147959999999</v>
+        <v>2.338480479999999</v>
       </c>
       <c r="P25">
-        <v>4.496417639999999</v>
+        <v>4.342892319999999</v>
       </c>
       <c r="Q25">
-        <v>10.34641764</v>
+        <v>10.19289232</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1095438614489741</v>
+        <v>0.1101367682052465</v>
       </c>
       <c r="T25">
-        <v>0.9275508536155038</v>
+        <v>0.9361783693541786</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.273382261182942</v>
+        <v>2.178658000300319</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09552874383598736</v>
+        <v>0.09537661435626471</v>
       </c>
       <c r="C26">
-        <v>207.3045859915567</v>
+        <v>204.9774811861433</v>
       </c>
       <c r="D26">
-        <v>257.0885859915567</v>
+        <v>257.8774811861433</v>
       </c>
       <c r="E26">
-        <v>-111.716</v>
+        <v>-108.6</v>
       </c>
       <c r="F26">
-        <v>74.78400000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G26">
         <v>25</v>
@@ -3413,28 +3413,28 @@
         <v>12.35</v>
       </c>
       <c r="M26">
-        <v>5.668627200000001</v>
+        <v>5.904820000000001</v>
       </c>
       <c r="N26">
-        <v>6.681372799999998</v>
+        <v>6.445179999999999</v>
       </c>
       <c r="O26">
-        <v>2.338480479999999</v>
+        <v>2.255812999999999</v>
       </c>
       <c r="P26">
-        <v>4.342892319999999</v>
+        <v>4.189366999999999</v>
       </c>
       <c r="Q26">
-        <v>10.19289232</v>
+        <v>10.039367</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1101367682052465</v>
+        <v>0.1107454858083529</v>
       </c>
       <c r="T26">
-        <v>0.9361783693541786</v>
+        <v>0.9450359521792182</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.178658000300319</v>
+        <v>2.091511680288306</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09537661435626471</v>
+        <v>0.09522448487654206</v>
       </c>
       <c r="C27">
-        <v>204.9774811861433</v>
+        <v>202.6552328487662</v>
       </c>
       <c r="D27">
-        <v>257.8774811861433</v>
+        <v>258.6712328487662</v>
       </c>
       <c r="E27">
-        <v>-108.6</v>
+        <v>-105.484</v>
       </c>
       <c r="F27">
-        <v>77.90000000000001</v>
+        <v>81.01600000000001</v>
       </c>
       <c r="G27">
         <v>25</v>
@@ -3495,28 +3495,28 @@
         <v>12.35</v>
       </c>
       <c r="M27">
-        <v>5.904820000000001</v>
+        <v>6.141012800000001</v>
       </c>
       <c r="N27">
-        <v>6.445179999999999</v>
+        <v>6.208987199999998</v>
       </c>
       <c r="O27">
-        <v>2.255812999999999</v>
+        <v>2.173145519999999</v>
       </c>
       <c r="P27">
-        <v>4.189366999999999</v>
+        <v>4.035841679999999</v>
       </c>
       <c r="Q27">
-        <v>10.039367</v>
+        <v>9.885841679999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1107454858083529</v>
+        <v>0.1113706552385703</v>
       </c>
       <c r="T27">
-        <v>0.9450359521792182</v>
+        <v>0.9541329291346642</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.091511680288306</v>
+        <v>2.011068923354141</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09522448487654206</v>
+        <v>0.09756445539681939</v>
       </c>
       <c r="C28">
-        <v>202.6552328487662</v>
+        <v>187.8462080758812</v>
       </c>
       <c r="D28">
-        <v>258.6712328487662</v>
+        <v>246.9782080758812</v>
       </c>
       <c r="E28">
-        <v>-105.484</v>
+        <v>-102.368</v>
       </c>
       <c r="F28">
-        <v>81.01600000000001</v>
+        <v>84.13200000000001</v>
       </c>
       <c r="G28">
         <v>25</v>
@@ -3577,45 +3577,45 @@
         <v>12.35</v>
       </c>
       <c r="M28">
-        <v>6.141012800000001</v>
+        <v>7.57188</v>
       </c>
       <c r="N28">
-        <v>6.208987199999998</v>
+        <v>4.778119999999999</v>
       </c>
       <c r="O28">
-        <v>2.173145519999999</v>
+        <v>1.672342</v>
       </c>
       <c r="P28">
-        <v>4.035841679999999</v>
+        <v>3.105778</v>
       </c>
       <c r="Q28">
-        <v>9.885841679999999</v>
+        <v>8.955777999999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1113706552385703</v>
+        <v>0.1120129525983827</v>
       </c>
       <c r="T28">
-        <v>0.9541329291346642</v>
+        <v>0.9634791383354649</v>
       </c>
       <c r="U28">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.011068923354141</v>
+        <v>1.631034828866807</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09756445539681939</v>
+        <v>0.09750462591709672</v>
       </c>
       <c r="C29">
-        <v>187.8462080758812</v>
+        <v>185.0159963864999</v>
       </c>
       <c r="D29">
-        <v>246.9782080758812</v>
+        <v>247.2639963864999</v>
       </c>
       <c r="E29">
-        <v>-102.368</v>
+        <v>-99.25200000000001</v>
       </c>
       <c r="F29">
-        <v>84.13200000000001</v>
+        <v>87.24800000000002</v>
       </c>
       <c r="G29">
         <v>25</v>
@@ -3659,28 +3659,28 @@
         <v>12.35</v>
       </c>
       <c r="M29">
-        <v>7.57188</v>
+        <v>7.852320000000002</v>
       </c>
       <c r="N29">
-        <v>4.778119999999999</v>
+        <v>4.497679999999998</v>
       </c>
       <c r="O29">
-        <v>1.672342</v>
+        <v>1.574187999999999</v>
       </c>
       <c r="P29">
-        <v>3.105778</v>
+        <v>2.923491999999999</v>
       </c>
       <c r="Q29">
-        <v>8.955777999999999</v>
+        <v>8.773491999999997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1120129525983827</v>
+        <v>0.1126730915515232</v>
       </c>
       <c r="T29">
-        <v>0.9634791383354649</v>
+        <v>0.97308496445851</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.631034828866807</v>
+        <v>1.572783584978707</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09750462591709672</v>
+        <v>0.09744479643737405</v>
       </c>
       <c r="C30">
-        <v>185.0159963864999</v>
+        <v>182.1864468573792</v>
       </c>
       <c r="D30">
-        <v>247.2639963864999</v>
+        <v>247.5504468573792</v>
       </c>
       <c r="E30">
-        <v>-99.25200000000001</v>
+        <v>-96.13600000000001</v>
       </c>
       <c r="F30">
-        <v>87.24800000000002</v>
+        <v>90.36400000000002</v>
       </c>
       <c r="G30">
         <v>25</v>
@@ -3741,28 +3741,28 @@
         <v>12.35</v>
       </c>
       <c r="M30">
-        <v>7.852320000000002</v>
+        <v>8.132760000000001</v>
       </c>
       <c r="N30">
-        <v>4.497679999999998</v>
+        <v>4.217239999999999</v>
       </c>
       <c r="O30">
-        <v>1.574187999999999</v>
+        <v>1.476033999999999</v>
       </c>
       <c r="P30">
-        <v>2.923491999999999</v>
+        <v>2.741205999999999</v>
       </c>
       <c r="Q30">
-        <v>8.773491999999997</v>
+        <v>8.591206</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1126730915515232</v>
+        <v>0.1133518259681325</v>
       </c>
       <c r="T30">
-        <v>0.97308496445851</v>
+        <v>0.9829613772329086</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.572783584978707</v>
+        <v>1.518549668255303</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09744479643737405</v>
+        <v>0.1105637400887922</v>
       </c>
       <c r="C31">
-        <v>182.1864468573793</v>
+        <v>128.9250976426362</v>
       </c>
       <c r="D31">
-        <v>247.5504468573792</v>
+        <v>197.4050976426362</v>
       </c>
       <c r="E31">
-        <v>-96.13600000000002</v>
+        <v>-93.02000000000002</v>
       </c>
       <c r="F31">
-        <v>90.364</v>
+        <v>93.48</v>
       </c>
       <c r="G31">
         <v>25</v>
@@ -3823,45 +3823,45 @@
         <v>12.35</v>
       </c>
       <c r="M31">
-        <v>8.132759999999999</v>
+        <v>13.722864</v>
       </c>
       <c r="N31">
-        <v>4.21724</v>
+        <v>-1.372864000000002</v>
       </c>
       <c r="O31">
-        <v>1.476034</v>
+        <v>-0.4805024000000006</v>
       </c>
       <c r="P31">
-        <v>2.741206</v>
+        <v>-0.8923616000000011</v>
       </c>
       <c r="Q31">
-        <v>8.591206</v>
+        <v>4.957638399999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1133518259681325</v>
+        <v>0.114850987583292</v>
       </c>
       <c r="T31">
-        <v>0.9829613772329086</v>
+        <v>1.004776005406351</v>
       </c>
       <c r="U31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.35</v>
+        <v>0.3149852683812941</v>
       </c>
       <c r="W31">
-        <v>0.0585</v>
+        <v>0.100560162601626</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.518549668255303</v>
+        <v>0.8999579096608403</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1105637400887922</v>
+        <v>0.1115737400887922</v>
       </c>
       <c r="C32">
-        <v>128.9250976426362</v>
+        <v>122.7778096491314</v>
       </c>
       <c r="D32">
-        <v>197.4050976426362</v>
+        <v>194.3738096491314</v>
       </c>
       <c r="E32">
-        <v>-93.02000000000002</v>
+        <v>-89.90400000000002</v>
       </c>
       <c r="F32">
-        <v>93.48</v>
+        <v>96.596</v>
       </c>
       <c r="G32">
         <v>25</v>
@@ -3905,37 +3905,37 @@
         <v>12.35</v>
       </c>
       <c r="M32">
-        <v>13.722864</v>
+        <v>14.1802928</v>
       </c>
       <c r="N32">
-        <v>-1.372864000000002</v>
+        <v>-1.830292800000002</v>
       </c>
       <c r="O32">
-        <v>-0.4805024000000006</v>
+        <v>-0.6406024800000008</v>
       </c>
       <c r="P32">
-        <v>-0.8923616000000011</v>
+        <v>-1.189690320000002</v>
       </c>
       <c r="Q32">
-        <v>4.957638399999999</v>
+        <v>4.660309679999998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.114850987583292</v>
+        <v>0.1158517265337745</v>
       </c>
       <c r="T32">
-        <v>1.004776005406351</v>
+        <v>1.019337976499196</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.3149852683812941</v>
+        <v>0.3048244532722201</v>
       </c>
       <c r="W32">
-        <v>0.100560162601626</v>
+        <v>0.1020517702596381</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8999579096608403</v>
+        <v>0.8709270093492003</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1115737400887922</v>
+        <v>0.1125837400887922</v>
       </c>
       <c r="C33">
-        <v>122.7778096491314</v>
+        <v>116.7222086701414</v>
       </c>
       <c r="D33">
-        <v>194.3738096491314</v>
+        <v>191.4342086701414</v>
       </c>
       <c r="E33">
-        <v>-89.90400000000002</v>
+        <v>-86.78800000000003</v>
       </c>
       <c r="F33">
-        <v>96.596</v>
+        <v>99.712</v>
       </c>
       <c r="G33">
         <v>25</v>
@@ -3987,37 +3987,37 @@
         <v>12.35</v>
       </c>
       <c r="M33">
-        <v>14.1802928</v>
+        <v>14.6377216</v>
       </c>
       <c r="N33">
-        <v>-1.830292800000002</v>
+        <v>-2.287721600000003</v>
       </c>
       <c r="O33">
-        <v>-0.6406024800000008</v>
+        <v>-0.800702560000001</v>
       </c>
       <c r="P33">
-        <v>-1.189690320000002</v>
+        <v>-1.487019040000002</v>
       </c>
       <c r="Q33">
-        <v>4.660309679999998</v>
+        <v>4.362980959999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1158517265337745</v>
+        <v>0.1168818989828006</v>
       </c>
       <c r="T33">
-        <v>1.019337976499196</v>
+        <v>1.034328240859479</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.3048244532722201</v>
+        <v>0.2952986891074632</v>
       </c>
       <c r="W33">
-        <v>0.1020517702596381</v>
+        <v>0.1034501524390244</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8709270093492003</v>
+        <v>0.8437105403070377</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1125837400887922</v>
+        <v>0.1135937400887922</v>
       </c>
       <c r="C34">
-        <v>116.7222086701414</v>
+        <v>110.7541968102911</v>
       </c>
       <c r="D34">
-        <v>191.4342086701414</v>
+        <v>188.5821968102911</v>
       </c>
       <c r="E34">
-        <v>-86.78800000000003</v>
+        <v>-83.67200000000001</v>
       </c>
       <c r="F34">
-        <v>99.712</v>
+        <v>102.828</v>
       </c>
       <c r="G34">
         <v>25</v>
@@ -4069,37 +4069,37 @@
         <v>12.35</v>
       </c>
       <c r="M34">
-        <v>14.6377216</v>
+        <v>15.0951504</v>
       </c>
       <c r="N34">
-        <v>-2.287721600000003</v>
+        <v>-2.745150400000004</v>
       </c>
       <c r="O34">
-        <v>-0.800702560000001</v>
+        <v>-0.9608026400000012</v>
       </c>
       <c r="P34">
-        <v>-1.487019040000002</v>
+        <v>-1.784347760000002</v>
       </c>
       <c r="Q34">
-        <v>4.362980959999998</v>
+        <v>4.065652239999997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1168818989828006</v>
+        <v>0.1179428228482155</v>
       </c>
       <c r="T34">
-        <v>1.034328240859479</v>
+        <v>1.04976597579768</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2952986891074632</v>
+        <v>0.2863502439829946</v>
       </c>
       <c r="W34">
-        <v>0.1034501524390244</v>
+        <v>0.1047637841832964</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8437105403070377</v>
+        <v>0.8181435542371275</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1135937400887922</v>
+        <v>0.1343202373109807</v>
       </c>
       <c r="C35">
-        <v>110.7541968102911</v>
+        <v>63.48277543911669</v>
       </c>
       <c r="D35">
-        <v>188.5821968102911</v>
+        <v>144.4267754391167</v>
       </c>
       <c r="E35">
-        <v>-83.67200000000001</v>
+        <v>-80.55600000000001</v>
       </c>
       <c r="F35">
-        <v>102.828</v>
+        <v>105.944</v>
       </c>
       <c r="G35">
         <v>25</v>
@@ -4151,45 +4151,45 @@
         <v>12.35</v>
       </c>
       <c r="M35">
-        <v>15.0951504</v>
+        <v>21.2735552</v>
       </c>
       <c r="N35">
-        <v>-2.745150400000004</v>
+        <v>-8.923555200000004</v>
       </c>
       <c r="O35">
-        <v>-0.9608026400000012</v>
+        <v>-3.123244320000001</v>
       </c>
       <c r="P35">
-        <v>-1.784347760000002</v>
+        <v>-5.800310880000003</v>
       </c>
       <c r="Q35">
-        <v>4.065652239999997</v>
+        <v>0.04968911999999648</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1179428228482155</v>
+        <v>0.121091194743171</v>
       </c>
       <c r="T35">
-        <v>1.04976597579768</v>
+        <v>1.095578623043763</v>
       </c>
       <c r="U35">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.2863502439829946</v>
+        <v>0.2031865364939095</v>
       </c>
       <c r="W35">
-        <v>0.1047637841832964</v>
+        <v>0.160000143472023</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8181435542371275</v>
+        <v>0.5805329614111701</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1343202373109807</v>
+        <v>0.1358702373109807</v>
       </c>
       <c r="C36">
-        <v>63.48277543911669</v>
+        <v>57.88136506812246</v>
       </c>
       <c r="D36">
-        <v>144.4267754391167</v>
+        <v>141.9413650681225</v>
       </c>
       <c r="E36">
-        <v>-80.55600000000001</v>
+        <v>-77.44000000000001</v>
       </c>
       <c r="F36">
-        <v>105.944</v>
+        <v>109.06</v>
       </c>
       <c r="G36">
         <v>25</v>
@@ -4233,37 +4233,37 @@
         <v>12.35</v>
       </c>
       <c r="M36">
-        <v>21.2735552</v>
+        <v>21.899248</v>
       </c>
       <c r="N36">
-        <v>-8.923555200000004</v>
+        <v>-9.549248000000004</v>
       </c>
       <c r="O36">
-        <v>-3.123244320000001</v>
+        <v>-3.342236800000001</v>
       </c>
       <c r="P36">
-        <v>-5.800310880000003</v>
+        <v>-6.207011200000003</v>
       </c>
       <c r="Q36">
-        <v>0.04968911999999648</v>
+        <v>-0.3570112000000032</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.121091194743171</v>
+        <v>0.1222495208161429</v>
       </c>
       <c r="T36">
-        <v>1.095578623043763</v>
+        <v>1.112433678782898</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.2031865364939095</v>
+        <v>0.1973812068797978</v>
       </c>
       <c r="W36">
-        <v>0.160000143472023</v>
+        <v>0.1611658536585366</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5805329614111701</v>
+        <v>0.563946305370851</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1358702373109807</v>
+        <v>0.1374202373109807</v>
       </c>
       <c r="C37">
-        <v>57.88136506812246</v>
+        <v>52.36404935106285</v>
       </c>
       <c r="D37">
-        <v>141.9413650681225</v>
+        <v>139.5400493510629</v>
       </c>
       <c r="E37">
-        <v>-77.44000000000001</v>
+        <v>-74.32400000000001</v>
       </c>
       <c r="F37">
-        <v>109.06</v>
+        <v>112.176</v>
       </c>
       <c r="G37">
         <v>25</v>
@@ -4315,37 +4315,37 @@
         <v>12.35</v>
       </c>
       <c r="M37">
-        <v>21.899248</v>
+        <v>22.5249408</v>
       </c>
       <c r="N37">
-        <v>-9.549248000000004</v>
+        <v>-10.1749408</v>
       </c>
       <c r="O37">
-        <v>-3.342236800000001</v>
+        <v>-3.561229280000001</v>
       </c>
       <c r="P37">
-        <v>-6.207011200000003</v>
+        <v>-6.613711520000003</v>
       </c>
       <c r="Q37">
-        <v>-0.3570112000000032</v>
+        <v>-0.7637115200000029</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1222495208161429</v>
+        <v>0.1234440445788951</v>
       </c>
       <c r="T37">
-        <v>1.112433678782898</v>
+        <v>1.129815455013881</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1973812068797978</v>
+        <v>0.1918983955775812</v>
       </c>
       <c r="W37">
-        <v>0.1611658536585366</v>
+        <v>0.1622668021680217</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.563946305370851</v>
+        <v>0.5482811302216607</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1374202373109807</v>
+        <v>0.1389702373109807</v>
       </c>
       <c r="C38">
-        <v>52.3640493510628</v>
+        <v>46.92663123797774</v>
       </c>
       <c r="D38">
-        <v>139.5400493510628</v>
+        <v>137.2186312379777</v>
       </c>
       <c r="E38">
-        <v>-74.32400000000003</v>
+        <v>-71.20800000000003</v>
       </c>
       <c r="F38">
-        <v>112.176</v>
+        <v>115.292</v>
       </c>
       <c r="G38">
         <v>25</v>
@@ -4397,37 +4397,37 @@
         <v>12.35</v>
       </c>
       <c r="M38">
-        <v>22.5249408</v>
+        <v>23.1506336</v>
       </c>
       <c r="N38">
-        <v>-10.1749408</v>
+        <v>-10.8006336</v>
       </c>
       <c r="O38">
-        <v>-3.56122928</v>
+        <v>-3.780221760000001</v>
       </c>
       <c r="P38">
-        <v>-6.613711520000001</v>
+        <v>-7.020411840000002</v>
       </c>
       <c r="Q38">
-        <v>-0.7637115200000011</v>
+        <v>-1.170411840000003</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1234440445788951</v>
+        <v>0.1246764897309411</v>
       </c>
       <c r="T38">
-        <v>1.12981545501388</v>
+        <v>1.147749033664894</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1918983955775813</v>
+        <v>0.1867119524538628</v>
       </c>
       <c r="W38">
-        <v>0.1622668021680217</v>
+        <v>0.1633082399472643</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5482811302216608</v>
+        <v>0.5334627212967509</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1389702373109807</v>
+        <v>0.1405202373109807</v>
       </c>
       <c r="C39">
-        <v>46.92663123797774</v>
+        <v>41.56518840066119</v>
       </c>
       <c r="D39">
-        <v>137.2186312379777</v>
+        <v>134.9731884006612</v>
       </c>
       <c r="E39">
-        <v>-71.20800000000003</v>
+        <v>-68.09200000000001</v>
       </c>
       <c r="F39">
-        <v>115.292</v>
+        <v>118.408</v>
       </c>
       <c r="G39">
         <v>25</v>
@@ -4479,37 +4479,37 @@
         <v>12.35</v>
       </c>
       <c r="M39">
-        <v>23.1506336</v>
+        <v>23.7763264</v>
       </c>
       <c r="N39">
-        <v>-10.8006336</v>
+        <v>-11.4263264</v>
       </c>
       <c r="O39">
-        <v>-3.780221760000001</v>
+        <v>-3.999214240000001</v>
       </c>
       <c r="P39">
-        <v>-7.020411840000002</v>
+        <v>-7.427112160000002</v>
       </c>
       <c r="Q39">
-        <v>-1.170411840000003</v>
+        <v>-1.577112160000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1246764897309411</v>
+        <v>0.1259486911782143</v>
       </c>
       <c r="T39">
-        <v>1.147749033664894</v>
+        <v>1.166261114853038</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1867119524538628</v>
+        <v>0.1817984800208664</v>
       </c>
       <c r="W39">
-        <v>0.1633082399472643</v>
+        <v>0.16429486521181</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5334627212967509</v>
+        <v>0.519424228631047</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1405202373109807</v>
+        <v>0.1420702373109807</v>
       </c>
       <c r="C40">
-        <v>41.56518840066119</v>
+        <v>36.27605111685848</v>
       </c>
       <c r="D40">
-        <v>134.9731884006612</v>
+        <v>132.8000511168585</v>
       </c>
       <c r="E40">
-        <v>-68.09200000000001</v>
+        <v>-64.97600000000001</v>
       </c>
       <c r="F40">
-        <v>118.408</v>
+        <v>121.524</v>
       </c>
       <c r="G40">
         <v>25</v>
@@ -4561,37 +4561,37 @@
         <v>12.35</v>
       </c>
       <c r="M40">
-        <v>23.7763264</v>
+        <v>24.40201920000001</v>
       </c>
       <c r="N40">
-        <v>-11.4263264</v>
+        <v>-12.05201920000001</v>
       </c>
       <c r="O40">
-        <v>-3.999214240000001</v>
+        <v>-4.218206720000001</v>
       </c>
       <c r="P40">
-        <v>-7.427112160000002</v>
+        <v>-7.833812480000004</v>
       </c>
       <c r="Q40">
-        <v>-1.577112160000002</v>
+        <v>-1.983812480000005</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1259486911782143</v>
+        <v>0.127262604148349</v>
       </c>
       <c r="T40">
-        <v>1.166261114853038</v>
+        <v>1.18538014952276</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1817984800208664</v>
+        <v>0.1771369805331519</v>
       </c>
       <c r="W40">
-        <v>0.16429486521181</v>
+        <v>0.1652308943089431</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.519424228631047</v>
+        <v>0.5061056586661483</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1420702373109807</v>
+        <v>0.1581676003248031</v>
       </c>
       <c r="C41">
-        <v>36.27605111685848</v>
+        <v>14.1356114660779</v>
       </c>
       <c r="D41">
-        <v>132.8000511168585</v>
+        <v>113.7756114660779</v>
       </c>
       <c r="E41">
-        <v>-64.97600000000001</v>
+        <v>-61.86000000000001</v>
       </c>
       <c r="F41">
-        <v>121.524</v>
+        <v>124.64</v>
       </c>
       <c r="G41">
         <v>25</v>
@@ -4643,45 +4643,45 @@
         <v>12.35</v>
       </c>
       <c r="M41">
-        <v>24.40201920000001</v>
+        <v>29.39011200000001</v>
       </c>
       <c r="N41">
-        <v>-12.05201920000001</v>
+        <v>-17.04011200000001</v>
       </c>
       <c r="O41">
-        <v>-4.218206720000001</v>
+        <v>-5.964039200000002</v>
       </c>
       <c r="P41">
-        <v>-7.833812480000004</v>
+        <v>-11.07607280000001</v>
       </c>
       <c r="Q41">
-        <v>-1.983812480000005</v>
+        <v>-5.226072800000006</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.127262604148349</v>
+        <v>0.1295325859071923</v>
       </c>
       <c r="T41">
-        <v>1.18538014952276</v>
+        <v>1.218411150002581</v>
       </c>
       <c r="U41">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.1771369805331519</v>
+        <v>0.1470732741678561</v>
       </c>
       <c r="W41">
-        <v>0.1652308943089431</v>
+        <v>0.2011201219512195</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.5061056586661483</v>
+        <v>0.4202093547653032</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1581676003248031</v>
+        <v>0.1600676003248032</v>
       </c>
       <c r="C42">
-        <v>14.1356114660779</v>
+        <v>9.127792077457869</v>
       </c>
       <c r="D42">
-        <v>113.7756114660779</v>
+        <v>111.8837920774579</v>
       </c>
       <c r="E42">
-        <v>-61.86000000000001</v>
+        <v>-58.74400000000001</v>
       </c>
       <c r="F42">
-        <v>124.64</v>
+        <v>127.756</v>
       </c>
       <c r="G42">
         <v>25</v>
@@ -4725,37 +4725,37 @@
         <v>12.35</v>
       </c>
       <c r="M42">
-        <v>29.39011200000001</v>
+        <v>30.1248648</v>
       </c>
       <c r="N42">
-        <v>-17.04011200000001</v>
+        <v>-17.7748648</v>
       </c>
       <c r="O42">
-        <v>-5.964039200000002</v>
+        <v>-6.221202680000001</v>
       </c>
       <c r="P42">
-        <v>-11.07607280000001</v>
+        <v>-11.55366212</v>
       </c>
       <c r="Q42">
-        <v>-5.226072800000006</v>
+        <v>-5.703662120000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1295325859071923</v>
+        <v>0.1309517822785006</v>
       </c>
       <c r="T42">
-        <v>1.218411150002581</v>
+        <v>1.239062186443303</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1470732741678561</v>
+        <v>0.1434861211393719</v>
       </c>
       <c r="W42">
-        <v>0.2011201219512195</v>
+        <v>0.2019659726353361</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4202093547653032</v>
+        <v>0.4099603461124911</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1600676003248032</v>
+        <v>0.1619676003248032</v>
       </c>
       <c r="C43">
-        <v>9.127792077457869</v>
+        <v>4.181856670745447</v>
       </c>
       <c r="D43">
-        <v>111.8837920774579</v>
+        <v>110.0538566707455</v>
       </c>
       <c r="E43">
-        <v>-58.74400000000001</v>
+        <v>-55.62800000000001</v>
       </c>
       <c r="F43">
-        <v>127.756</v>
+        <v>130.872</v>
       </c>
       <c r="G43">
         <v>25</v>
@@ -4807,37 +4807,37 @@
         <v>12.35</v>
       </c>
       <c r="M43">
-        <v>30.1248648</v>
+        <v>30.8596176</v>
       </c>
       <c r="N43">
-        <v>-17.7748648</v>
+        <v>-18.50961760000001</v>
       </c>
       <c r="O43">
-        <v>-6.221202680000001</v>
+        <v>-6.478366160000002</v>
       </c>
       <c r="P43">
-        <v>-11.55366212</v>
+        <v>-12.03125144</v>
       </c>
       <c r="Q43">
-        <v>-5.703662120000002</v>
+        <v>-6.181251440000004</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1309517822785006</v>
+        <v>0.1324199164557161</v>
       </c>
       <c r="T43">
-        <v>1.239062186443303</v>
+        <v>1.260425327588877</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1434861211393719</v>
+        <v>0.1400697849217677</v>
       </c>
       <c r="W43">
-        <v>0.2019659726353361</v>
+        <v>0.2027715447154472</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4099603461124911</v>
+        <v>0.4001993854907651</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1619676003248032</v>
+        <v>0.1638676003248031</v>
       </c>
       <c r="C44">
-        <v>4.181856670745447</v>
+        <v>-0.7051823535014137</v>
       </c>
       <c r="D44">
-        <v>110.0538566707455</v>
+        <v>108.2828176464986</v>
       </c>
       <c r="E44">
-        <v>-55.62800000000001</v>
+        <v>-52.51200000000003</v>
       </c>
       <c r="F44">
-        <v>130.872</v>
+        <v>133.988</v>
       </c>
       <c r="G44">
         <v>25</v>
@@ -4889,37 +4889,37 @@
         <v>12.35</v>
       </c>
       <c r="M44">
-        <v>30.8596176</v>
+        <v>31.5943704</v>
       </c>
       <c r="N44">
-        <v>-18.50961760000001</v>
+        <v>-19.2443704</v>
       </c>
       <c r="O44">
-        <v>-6.478366160000002</v>
+        <v>-6.73552964</v>
       </c>
       <c r="P44">
-        <v>-12.03125144</v>
+        <v>-12.50884076</v>
       </c>
       <c r="Q44">
-        <v>-6.181251440000004</v>
+        <v>-6.658840760000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1324199164557161</v>
+        <v>0.1339395641128339</v>
       </c>
       <c r="T44">
-        <v>1.260425327588877</v>
+        <v>1.282538052634296</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1400697849217677</v>
+        <v>0.136812348063122</v>
       </c>
       <c r="W44">
-        <v>0.2027715447154472</v>
+        <v>0.2035396483267158</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4001993854907651</v>
+        <v>0.3908924230374915</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1638676003248031</v>
+        <v>0.1657676003248032</v>
       </c>
       <c r="C45">
-        <v>-0.7051823535014137</v>
+        <v>-5.536123328992602</v>
       </c>
       <c r="D45">
-        <v>108.2828176464986</v>
+        <v>106.5678766710074</v>
       </c>
       <c r="E45">
-        <v>-52.51200000000003</v>
+        <v>-49.39600000000002</v>
       </c>
       <c r="F45">
-        <v>133.988</v>
+        <v>137.104</v>
       </c>
       <c r="G45">
         <v>25</v>
@@ -4971,37 +4971,37 @@
         <v>12.35</v>
       </c>
       <c r="M45">
-        <v>31.5943704</v>
+        <v>32.32912320000001</v>
       </c>
       <c r="N45">
-        <v>-19.2443704</v>
+        <v>-19.9791232</v>
       </c>
       <c r="O45">
-        <v>-6.73552964</v>
+        <v>-6.992693120000001</v>
       </c>
       <c r="P45">
-        <v>-12.50884076</v>
+        <v>-12.98643008</v>
       </c>
       <c r="Q45">
-        <v>-6.658840760000002</v>
+        <v>-7.136430080000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1339395641128339</v>
+        <v>0.1355134849005631</v>
       </c>
       <c r="T45">
-        <v>1.282538052634296</v>
+        <v>1.305440517859908</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.136812348063122</v>
+        <v>0.1337029765162329</v>
       </c>
       <c r="W45">
-        <v>0.2035396483267158</v>
+        <v>0.2042728381374723</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3908924230374915</v>
+        <v>0.382008504332094</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1657676003248032</v>
+        <v>0.1676676003248032</v>
       </c>
       <c r="C46">
-        <v>-5.536123328992602</v>
+        <v>-10.313590077622</v>
       </c>
       <c r="D46">
-        <v>106.5678766710074</v>
+        <v>104.906409922378</v>
       </c>
       <c r="E46">
-        <v>-49.39600000000002</v>
+        <v>-46.28</v>
       </c>
       <c r="F46">
-        <v>137.104</v>
+        <v>140.22</v>
       </c>
       <c r="G46">
         <v>25</v>
@@ -5053,37 +5053,37 @@
         <v>12.35</v>
       </c>
       <c r="M46">
-        <v>32.32912320000001</v>
+        <v>33.06387600000001</v>
       </c>
       <c r="N46">
-        <v>-19.9791232</v>
+        <v>-20.71387600000001</v>
       </c>
       <c r="O46">
-        <v>-6.992693120000001</v>
+        <v>-7.249856600000002</v>
       </c>
       <c r="P46">
-        <v>-12.98643008</v>
+        <v>-13.46401940000001</v>
       </c>
       <c r="Q46">
-        <v>-7.136430080000002</v>
+        <v>-7.614019400000005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1355134849005631</v>
+        <v>0.1371446391714825</v>
       </c>
       <c r="T46">
-        <v>1.305440517859908</v>
+        <v>1.329175800002816</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1337029765162329</v>
+        <v>0.1307317992603166</v>
       </c>
       <c r="W46">
-        <v>0.2042728381374723</v>
+        <v>0.2049734417344174</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.382008504332094</v>
+        <v>0.3735194264580474</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1676676003248032</v>
+        <v>0.1695676003248032</v>
       </c>
       <c r="C47">
-        <v>-10.313590077622</v>
+        <v>-15.04004530442961</v>
       </c>
       <c r="D47">
-        <v>104.906409922378</v>
+        <v>103.2959546955704</v>
       </c>
       <c r="E47">
-        <v>-46.28</v>
+        <v>-43.16400000000002</v>
       </c>
       <c r="F47">
-        <v>140.22</v>
+        <v>143.336</v>
       </c>
       <c r="G47">
         <v>25</v>
@@ -5135,37 +5135,37 @@
         <v>12.35</v>
       </c>
       <c r="M47">
-        <v>33.06387600000001</v>
+        <v>33.7986288</v>
       </c>
       <c r="N47">
-        <v>-20.71387600000001</v>
+        <v>-21.4486288</v>
       </c>
       <c r="O47">
-        <v>-7.249856600000002</v>
+        <v>-7.50702008</v>
       </c>
       <c r="P47">
-        <v>-13.46401940000001</v>
+        <v>-13.94160872</v>
       </c>
       <c r="Q47">
-        <v>-7.614019400000005</v>
+        <v>-8.091608720000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1371446391714825</v>
+        <v>0.1388362065635469</v>
       </c>
       <c r="T47">
-        <v>1.329175800002816</v>
+        <v>1.353790166669534</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1307317992603166</v>
+        <v>0.1278898036242228</v>
       </c>
       <c r="W47">
-        <v>0.2049734417344174</v>
+        <v>0.2056435843054083</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3735194264580474</v>
+        <v>0.3653994389263507</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1695676003248032</v>
+        <v>0.1714676003248032</v>
       </c>
       <c r="C48">
-        <v>-15.04004530442961</v>
+        <v>-19.71780277743238</v>
       </c>
       <c r="D48">
-        <v>103.2959546955704</v>
+        <v>101.7341972225676</v>
       </c>
       <c r="E48">
-        <v>-43.16400000000002</v>
+        <v>-40.048</v>
       </c>
       <c r="F48">
-        <v>143.336</v>
+        <v>146.452</v>
       </c>
       <c r="G48">
         <v>25</v>
@@ -5217,37 +5217,37 @@
         <v>12.35</v>
       </c>
       <c r="M48">
-        <v>33.7986288</v>
+        <v>34.53338160000001</v>
       </c>
       <c r="N48">
-        <v>-21.4486288</v>
+        <v>-22.1833816</v>
       </c>
       <c r="O48">
-        <v>-7.50702008</v>
+        <v>-7.764183560000001</v>
       </c>
       <c r="P48">
-        <v>-13.94160872</v>
+        <v>-14.41919804</v>
       </c>
       <c r="Q48">
-        <v>-8.091608720000002</v>
+        <v>-8.569198040000003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1388362065635469</v>
+        <v>0.1405916066873875</v>
       </c>
       <c r="T48">
-        <v>1.353790166669534</v>
+        <v>1.379333377361412</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1278898036242228</v>
+        <v>0.1251687439726435</v>
       </c>
       <c r="W48">
-        <v>0.2056435843054083</v>
+        <v>0.2062852101712506</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3653994389263507</v>
+        <v>0.3576249827789816</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1714676003248032</v>
+        <v>0.1733676003248032</v>
       </c>
       <c r="C49">
-        <v>-19.71780277743238</v>
+        <v>-24.34903841901163</v>
       </c>
       <c r="D49">
-        <v>101.7341972225676</v>
+        <v>100.2189615809884</v>
       </c>
       <c r="E49">
-        <v>-40.048</v>
+        <v>-36.93200000000002</v>
       </c>
       <c r="F49">
-        <v>146.452</v>
+        <v>149.568</v>
       </c>
       <c r="G49">
         <v>25</v>
@@ -5299,37 +5299,37 @@
         <v>12.35</v>
       </c>
       <c r="M49">
-        <v>34.53338160000001</v>
+        <v>35.2681344</v>
       </c>
       <c r="N49">
-        <v>-22.1833816</v>
+        <v>-22.9181344</v>
       </c>
       <c r="O49">
-        <v>-7.764183560000001</v>
+        <v>-8.02134704</v>
       </c>
       <c r="P49">
-        <v>-14.41919804</v>
+        <v>-14.89678736</v>
       </c>
       <c r="Q49">
-        <v>-8.569198040000003</v>
+        <v>-9.04678736</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1405916066873875</v>
+        <v>0.1424145222006065</v>
       </c>
       <c r="T49">
-        <v>1.379333377361412</v>
+        <v>1.405859019233747</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1251687439726435</v>
+        <v>0.1225610618065468</v>
       </c>
       <c r="W49">
-        <v>0.2062852101712506</v>
+        <v>0.2069001016260163</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3576249827789816</v>
+        <v>0.3501744623044195</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1733676003248031</v>
+        <v>0.1752676003248032</v>
       </c>
       <c r="C50">
-        <v>-24.34903841901161</v>
+        <v>-28.93580042067201</v>
       </c>
       <c r="D50">
-        <v>100.2189615809884</v>
+        <v>98.74819957932799</v>
       </c>
       <c r="E50">
-        <v>-36.93200000000002</v>
+        <v>-33.81600000000003</v>
       </c>
       <c r="F50">
-        <v>149.568</v>
+        <v>152.684</v>
       </c>
       <c r="G50">
         <v>25</v>
@@ -5381,37 +5381,37 @@
         <v>12.35</v>
       </c>
       <c r="M50">
-        <v>35.2681344</v>
+        <v>36.0028872</v>
       </c>
       <c r="N50">
-        <v>-22.9181344</v>
+        <v>-23.6528872</v>
       </c>
       <c r="O50">
-        <v>-8.02134704</v>
+        <v>-8.278510520000001</v>
       </c>
       <c r="P50">
-        <v>-14.89678736</v>
+        <v>-15.37437668</v>
       </c>
       <c r="Q50">
-        <v>-9.04678736</v>
+        <v>-9.524376680000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1424145222006064</v>
+        <v>0.1443089245966968</v>
       </c>
       <c r="T50">
-        <v>1.405859019233747</v>
+        <v>1.433424882355978</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1225610618065468</v>
+        <v>0.1200598156472295</v>
       </c>
       <c r="W50">
-        <v>0.2069001016260163</v>
+        <v>0.2074898954703833</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3501744623044195</v>
+        <v>0.3430280447063702</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1752676003248032</v>
+        <v>0.1771676003248032</v>
       </c>
       <c r="C51">
-        <v>-28.93580042067201</v>
+        <v>-33.48001848004763</v>
       </c>
       <c r="D51">
-        <v>98.74819957932799</v>
+        <v>97.31998151995238</v>
       </c>
       <c r="E51">
-        <v>-33.81600000000003</v>
+        <v>-30.70000000000002</v>
       </c>
       <c r="F51">
-        <v>152.684</v>
+        <v>155.8</v>
       </c>
       <c r="G51">
         <v>25</v>
@@ -5463,37 +5463,37 @@
         <v>12.35</v>
       </c>
       <c r="M51">
-        <v>36.0028872</v>
+        <v>36.73764000000001</v>
       </c>
       <c r="N51">
-        <v>-23.6528872</v>
+        <v>-24.38764</v>
       </c>
       <c r="O51">
-        <v>-8.278510520000001</v>
+        <v>-8.535674</v>
       </c>
       <c r="P51">
-        <v>-15.37437668</v>
+        <v>-15.851966</v>
       </c>
       <c r="Q51">
-        <v>-9.524376680000001</v>
+        <v>-10.001966</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1443089245966968</v>
+        <v>0.1462791030886307</v>
       </c>
       <c r="T51">
-        <v>1.433424882355978</v>
+        <v>1.462093380003097</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1200598156472295</v>
+        <v>0.1176586193342849</v>
       </c>
       <c r="W51">
-        <v>0.2074898954703833</v>
+        <v>0.2080560975609756</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3430280447063702</v>
+        <v>0.3361674838122427</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1771676003248032</v>
+        <v>0.1790676003248032</v>
       </c>
       <c r="C52">
-        <v>-33.48001848004763</v>
+        <v>-37.98351224775452</v>
       </c>
       <c r="D52">
-        <v>97.31998151995238</v>
+        <v>95.93248775224551</v>
       </c>
       <c r="E52">
-        <v>-30.70000000000002</v>
+        <v>-27.584</v>
       </c>
       <c r="F52">
-        <v>155.8</v>
+        <v>158.916</v>
       </c>
       <c r="G52">
         <v>25</v>
@@ -5545,37 +5545,37 @@
         <v>12.35</v>
       </c>
       <c r="M52">
-        <v>36.73764000000001</v>
+        <v>37.47239280000001</v>
       </c>
       <c r="N52">
-        <v>-24.38764</v>
+        <v>-25.12239280000001</v>
       </c>
       <c r="O52">
-        <v>-8.535674</v>
+        <v>-8.792837480000001</v>
       </c>
       <c r="P52">
-        <v>-15.851966</v>
+        <v>-16.32955532</v>
       </c>
       <c r="Q52">
-        <v>-10.001966</v>
+        <v>-10.47955532</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1462791030886307</v>
+        <v>0.148329697029215</v>
       </c>
       <c r="T52">
-        <v>1.462093380003097</v>
+        <v>1.491932020411324</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1176586193342849</v>
+        <v>0.1153515875826323</v>
       </c>
       <c r="W52">
-        <v>0.2080560975609756</v>
+        <v>0.2086000956480153</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3361674838122427</v>
+        <v>0.3295759645218065</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1790676003248032</v>
+        <v>0.1809676003248032</v>
       </c>
       <c r="C53">
-        <v>-37.98351224775452</v>
+        <v>-42.44799906183771</v>
       </c>
       <c r="D53">
-        <v>95.93248775224551</v>
+        <v>94.5840009381623</v>
       </c>
       <c r="E53">
-        <v>-27.584</v>
+        <v>-24.46800000000002</v>
       </c>
       <c r="F53">
-        <v>158.916</v>
+        <v>162.032</v>
       </c>
       <c r="G53">
         <v>25</v>
@@ -5627,37 +5627,37 @@
         <v>12.35</v>
       </c>
       <c r="M53">
-        <v>37.47239280000001</v>
+        <v>38.2071456</v>
       </c>
       <c r="N53">
-        <v>-25.12239280000001</v>
+        <v>-25.8571456</v>
       </c>
       <c r="O53">
-        <v>-8.792837480000001</v>
+        <v>-9.05000096</v>
       </c>
       <c r="P53">
-        <v>-16.32955532</v>
+        <v>-16.80714464</v>
       </c>
       <c r="Q53">
-        <v>-10.47955532</v>
+        <v>-10.95714464</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.148329697029215</v>
+        <v>0.1504657323839903</v>
       </c>
       <c r="T53">
-        <v>1.491932020411324</v>
+        <v>1.523013937503226</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1153515875826323</v>
+        <v>0.1131332878214278</v>
       </c>
       <c r="W53">
-        <v>0.2086000956480153</v>
+        <v>0.2091231707317073</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3295759645218065</v>
+        <v>0.3232379652040795</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1809676003248032</v>
+        <v>0.1828676003248032</v>
       </c>
       <c r="C54">
-        <v>-42.44799906183771</v>
+        <v>-46.87510103893995</v>
       </c>
       <c r="D54">
-        <v>94.5840009381623</v>
+        <v>93.27289896106008</v>
       </c>
       <c r="E54">
-        <v>-24.46800000000002</v>
+        <v>-21.352</v>
       </c>
       <c r="F54">
-        <v>162.032</v>
+        <v>165.148</v>
       </c>
       <c r="G54">
         <v>25</v>
@@ -5709,37 +5709,37 @@
         <v>12.35</v>
       </c>
       <c r="M54">
-        <v>38.2071456</v>
+        <v>38.94189840000001</v>
       </c>
       <c r="N54">
-        <v>-25.8571456</v>
+        <v>-26.59189840000001</v>
       </c>
       <c r="O54">
-        <v>-9.05000096</v>
+        <v>-9.307164440000001</v>
       </c>
       <c r="P54">
-        <v>-16.80714464</v>
+        <v>-17.28473396</v>
       </c>
       <c r="Q54">
-        <v>-10.95714464</v>
+        <v>-11.43473396</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1504657323839903</v>
+        <v>0.1526926628602454</v>
       </c>
       <c r="T54">
-        <v>1.523013937503226</v>
+        <v>1.555418489364997</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1131332878214278</v>
+        <v>0.1109986974851744</v>
       </c>
       <c r="W54">
-        <v>0.2091231707317073</v>
+        <v>0.2096265071329959</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3232379652040795</v>
+        <v>0.3171391356719271</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1828676003248032</v>
+        <v>0.1847676003248032</v>
       </c>
       <c r="C55">
-        <v>-46.87510103893995</v>
+        <v>-51.26635158375618</v>
       </c>
       <c r="D55">
-        <v>93.27289896106008</v>
+        <v>91.99764841624383</v>
       </c>
       <c r="E55">
-        <v>-21.352</v>
+        <v>-18.23600000000002</v>
       </c>
       <c r="F55">
-        <v>165.148</v>
+        <v>168.264</v>
       </c>
       <c r="G55">
         <v>25</v>
@@ -5791,37 +5791,37 @@
         <v>12.35</v>
       </c>
       <c r="M55">
-        <v>38.94189840000001</v>
+        <v>39.6766512</v>
       </c>
       <c r="N55">
-        <v>-26.59189840000001</v>
+        <v>-27.3266512</v>
       </c>
       <c r="O55">
-        <v>-9.307164440000001</v>
+        <v>-9.56432792</v>
       </c>
       <c r="P55">
-        <v>-17.28473396</v>
+        <v>-17.76232328</v>
       </c>
       <c r="Q55">
-        <v>-11.43473396</v>
+        <v>-11.91232328</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1526926628602454</v>
+        <v>0.1550164164006856</v>
       </c>
       <c r="T55">
-        <v>1.555418489364997</v>
+        <v>1.589231934785975</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1109986974851744</v>
+        <v>0.1089431660502638</v>
       </c>
       <c r="W55">
-        <v>0.2096265071329959</v>
+        <v>0.2101112014453478</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3171391356719271</v>
+        <v>0.3112661887150395</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1847676003248032</v>
+        <v>0.1866676003248032</v>
       </c>
       <c r="C56">
-        <v>-51.26635158375618</v>
+        <v>-55.62320137169773</v>
       </c>
       <c r="D56">
-        <v>91.99764841624383</v>
+        <v>90.75679862830229</v>
       </c>
       <c r="E56">
-        <v>-18.23600000000002</v>
+        <v>-15.12</v>
       </c>
       <c r="F56">
-        <v>168.264</v>
+        <v>171.38</v>
       </c>
       <c r="G56">
         <v>25</v>
@@ -5873,37 +5873,37 @@
         <v>12.35</v>
       </c>
       <c r="M56">
-        <v>39.6766512</v>
+        <v>40.411404</v>
       </c>
       <c r="N56">
-        <v>-27.3266512</v>
+        <v>-28.061404</v>
       </c>
       <c r="O56">
-        <v>-9.56432792</v>
+        <v>-9.821491400000001</v>
       </c>
       <c r="P56">
-        <v>-17.76232328</v>
+        <v>-18.2399126</v>
       </c>
       <c r="Q56">
-        <v>-11.91232328</v>
+        <v>-12.3899126</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1550164164006856</v>
+        <v>0.1574434478762563</v>
       </c>
       <c r="T56">
-        <v>1.589231934785975</v>
+        <v>1.624548200003441</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1089431660502638</v>
+        <v>0.1069623812129863</v>
       </c>
       <c r="W56">
-        <v>0.2101112014453478</v>
+        <v>0.2105782705099778</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3112661887150395</v>
+        <v>0.3056068034656751</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1866676003248032</v>
+        <v>0.1885676003248032</v>
       </c>
       <c r="C57">
-        <v>-55.62320137169773</v>
+        <v>-59.94702385383985</v>
       </c>
       <c r="D57">
-        <v>90.75679862830229</v>
+        <v>89.54897614616019</v>
       </c>
       <c r="E57">
-        <v>-15.12</v>
+        <v>-12.00399999999999</v>
       </c>
       <c r="F57">
-        <v>171.38</v>
+        <v>174.496</v>
       </c>
       <c r="G57">
         <v>25</v>
@@ -5955,37 +5955,37 @@
         <v>12.35</v>
       </c>
       <c r="M57">
-        <v>40.411404</v>
+        <v>41.14615680000001</v>
       </c>
       <c r="N57">
-        <v>-28.061404</v>
+        <v>-28.79615680000001</v>
       </c>
       <c r="O57">
-        <v>-9.821491400000001</v>
+        <v>-10.07865488</v>
       </c>
       <c r="P57">
-        <v>-18.2399126</v>
+        <v>-18.71750192</v>
       </c>
       <c r="Q57">
-        <v>-12.3899126</v>
+        <v>-12.86750192</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1574434478762563</v>
+        <v>0.1599807989643531</v>
       </c>
       <c r="T57">
-        <v>1.624548200003441</v>
+        <v>1.66146975000352</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1069623812129863</v>
+        <v>0.1050523386913258</v>
       </c>
       <c r="W57">
-        <v>0.2105782705099778</v>
+        <v>0.2110286585365854</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3056068034656751</v>
+        <v>0.3001495391180738</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1885676003248032</v>
+        <v>0.1904676003248032</v>
       </c>
       <c r="C58">
-        <v>-59.94702385383985</v>
+        <v>-64.23912032807253</v>
       </c>
       <c r="D58">
-        <v>89.54897614616019</v>
+        <v>88.37287967192749</v>
       </c>
       <c r="E58">
-        <v>-12.00399999999999</v>
+        <v>-8.888000000000005</v>
       </c>
       <c r="F58">
-        <v>174.496</v>
+        <v>177.612</v>
       </c>
       <c r="G58">
         <v>25</v>
@@ -6037,37 +6037,37 @@
         <v>12.35</v>
       </c>
       <c r="M58">
-        <v>41.14615680000001</v>
+        <v>41.88090960000001</v>
       </c>
       <c r="N58">
-        <v>-28.79615680000001</v>
+        <v>-29.53090960000001</v>
       </c>
       <c r="O58">
-        <v>-10.07865488</v>
+        <v>-10.33581836</v>
       </c>
       <c r="P58">
-        <v>-18.71750192</v>
+        <v>-19.19509124</v>
       </c>
       <c r="Q58">
-        <v>-12.86750192</v>
+        <v>-13.34509124</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1599807989643531</v>
+        <v>0.1626361663821287</v>
       </c>
       <c r="T58">
-        <v>1.66146975000352</v>
+        <v>1.70010858139895</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1050523386913258</v>
+        <v>0.1032093152055131</v>
       </c>
       <c r="W58">
-        <v>0.2110286585365854</v>
+        <v>0.21146324347454</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3001495391180738</v>
+        <v>0.2948837577300374</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1904676003248032</v>
+        <v>0.1923676003248032</v>
       </c>
       <c r="C59">
-        <v>-64.23912032807253</v>
+        <v>-68.50072461581806</v>
       </c>
       <c r="D59">
-        <v>88.37287967192749</v>
+        <v>87.22727538418198</v>
       </c>
       <c r="E59">
-        <v>-8.888000000000005</v>
+        <v>-5.771999999999991</v>
       </c>
       <c r="F59">
-        <v>177.612</v>
+        <v>180.728</v>
       </c>
       <c r="G59">
         <v>25</v>
@@ -6119,37 +6119,37 @@
         <v>12.35</v>
       </c>
       <c r="M59">
-        <v>41.88090960000001</v>
+        <v>42.61566240000001</v>
       </c>
       <c r="N59">
-        <v>-29.53090960000001</v>
+        <v>-30.26566240000001</v>
       </c>
       <c r="O59">
-        <v>-10.33581836</v>
+        <v>-10.59298184</v>
       </c>
       <c r="P59">
-        <v>-19.19509124</v>
+        <v>-19.67268056000001</v>
       </c>
       <c r="Q59">
-        <v>-13.34509124</v>
+        <v>-13.82268056000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1626361663821287</v>
+        <v>0.1654179798674175</v>
       </c>
       <c r="T59">
-        <v>1.70010858139895</v>
+        <v>1.740587357146544</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1032093152055131</v>
+        <v>0.1014298442536939</v>
       </c>
       <c r="W59">
-        <v>0.21146324347454</v>
+        <v>0.211882842724979</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2948837577300374</v>
+        <v>0.289799555010554</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1923676003248032</v>
+        <v>0.1942676003248032</v>
       </c>
       <c r="C60">
-        <v>-68.500724615818</v>
+        <v>-72.73300737964908</v>
       </c>
       <c r="D60">
-        <v>87.22727538418201</v>
+        <v>86.11099262035091</v>
       </c>
       <c r="E60">
-        <v>-5.77200000000002</v>
+        <v>-2.656000000000034</v>
       </c>
       <c r="F60">
-        <v>180.728</v>
+        <v>183.844</v>
       </c>
       <c r="G60">
         <v>25</v>
@@ -6201,37 +6201,37 @@
         <v>12.35</v>
       </c>
       <c r="M60">
-        <v>42.61566240000001</v>
+        <v>43.3504152</v>
       </c>
       <c r="N60">
-        <v>-30.2656624</v>
+        <v>-31.0004152</v>
       </c>
       <c r="O60">
-        <v>-10.59298184</v>
+        <v>-10.85014532</v>
       </c>
       <c r="P60">
-        <v>-19.67268056</v>
+        <v>-20.15026988</v>
       </c>
       <c r="Q60">
-        <v>-13.82268056</v>
+        <v>-14.30026988</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1654179798674175</v>
+        <v>0.1683354915715009</v>
       </c>
       <c r="T60">
-        <v>1.740587357146544</v>
+        <v>1.78304070732085</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1014298442536939</v>
+        <v>0.09971069435108892</v>
       </c>
       <c r="W60">
-        <v>0.211882842724979</v>
+        <v>0.2122882182720132</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2897995550105541</v>
+        <v>0.2848876981459684</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1942676003248032</v>
+        <v>0.1961676003248032</v>
       </c>
       <c r="C61">
-        <v>-72.73300737964908</v>
+        <v>-76.93708011357089</v>
       </c>
       <c r="D61">
-        <v>86.11099262035091</v>
+        <v>85.02291988642912</v>
       </c>
       <c r="E61">
-        <v>-2.656000000000034</v>
+        <v>0.4599999999999795</v>
       </c>
       <c r="F61">
-        <v>183.844</v>
+        <v>186.96</v>
       </c>
       <c r="G61">
         <v>25</v>
@@ -6283,37 +6283,37 @@
         <v>12.35</v>
       </c>
       <c r="M61">
-        <v>43.3504152</v>
+        <v>44.085168</v>
       </c>
       <c r="N61">
-        <v>-31.0004152</v>
+        <v>-31.735168</v>
       </c>
       <c r="O61">
-        <v>-10.85014532</v>
+        <v>-11.1073088</v>
       </c>
       <c r="P61">
-        <v>-20.15026988</v>
+        <v>-20.6278592</v>
       </c>
       <c r="Q61">
-        <v>-14.30026988</v>
+        <v>-14.7778592</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1683354915715009</v>
+        <v>0.1713988788607884</v>
       </c>
       <c r="T61">
-        <v>1.78304070732085</v>
+        <v>1.827616725003872</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09971069435108892</v>
+        <v>0.09804884944523744</v>
       </c>
       <c r="W61">
-        <v>0.2122882182720132</v>
+        <v>0.212680081300813</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2848876981459684</v>
+        <v>0.2801395698435356</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1961676003248032</v>
+        <v>0.1980676003248032</v>
       </c>
       <c r="C62">
-        <v>-76.93708011357089</v>
+        <v>-81.11399883455702</v>
       </c>
       <c r="D62">
-        <v>85.02291988642912</v>
+        <v>83.962001165443</v>
       </c>
       <c r="E62">
-        <v>0.4599999999999795</v>
+        <v>3.575999999999993</v>
       </c>
       <c r="F62">
-        <v>186.96</v>
+        <v>190.076</v>
       </c>
       <c r="G62">
         <v>25</v>
@@ -6365,37 +6365,37 @@
         <v>12.35</v>
       </c>
       <c r="M62">
-        <v>44.085168</v>
+        <v>44.81992080000001</v>
       </c>
       <c r="N62">
-        <v>-31.735168</v>
+        <v>-32.4699208</v>
       </c>
       <c r="O62">
-        <v>-11.1073088</v>
+        <v>-11.36447228</v>
       </c>
       <c r="P62">
-        <v>-20.6278592</v>
+        <v>-21.10544852</v>
       </c>
       <c r="Q62">
-        <v>-14.7778592</v>
+        <v>-15.25544852</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1713988788607884</v>
+        <v>0.1746193629341419</v>
       </c>
       <c r="T62">
-        <v>1.827616725003872</v>
+        <v>1.874478692311663</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09804884944523744</v>
+        <v>0.09644149125761059</v>
       </c>
       <c r="W62">
-        <v>0.212680081300813</v>
+        <v>0.2130590963614554</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2801395698435356</v>
+        <v>0.2755471178788874</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1980676003248032</v>
+        <v>0.1999676003248032</v>
       </c>
       <c r="C63">
-        <v>-81.11399883455702</v>
+        <v>-85.2647675011137</v>
       </c>
       <c r="D63">
-        <v>83.962001165443</v>
+        <v>82.92723249888631</v>
       </c>
       <c r="E63">
-        <v>3.575999999999993</v>
+        <v>6.691999999999979</v>
       </c>
       <c r="F63">
-        <v>190.076</v>
+        <v>193.192</v>
       </c>
       <c r="G63">
         <v>25</v>
@@ -6447,37 +6447,37 @@
         <v>12.35</v>
       </c>
       <c r="M63">
-        <v>44.81992080000001</v>
+        <v>45.5546736</v>
       </c>
       <c r="N63">
-        <v>-32.4699208</v>
+        <v>-33.2046736</v>
       </c>
       <c r="O63">
-        <v>-11.36447228</v>
+        <v>-11.62163576</v>
       </c>
       <c r="P63">
-        <v>-21.10544852</v>
+        <v>-21.58303784</v>
       </c>
       <c r="Q63">
-        <v>-15.25544852</v>
+        <v>-15.73303784</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1746193629341419</v>
+        <v>0.1780093461692509</v>
       </c>
       <c r="T63">
-        <v>1.874478692311663</v>
+        <v>1.923807078951444</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09644149125761059</v>
+        <v>0.09488598333410075</v>
       </c>
       <c r="W63">
-        <v>0.2130590963614554</v>
+        <v>0.2134258851298191</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2755471178788874</v>
+        <v>0.2711028095260022</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1999676003248032</v>
+        <v>0.2018676003248032</v>
       </c>
       <c r="C64">
-        <v>-85.2647675011137</v>
+        <v>-89.39034118213381</v>
       </c>
       <c r="D64">
-        <v>82.92723249888631</v>
+        <v>81.91765881786621</v>
       </c>
       <c r="E64">
-        <v>6.691999999999979</v>
+        <v>9.807999999999993</v>
       </c>
       <c r="F64">
-        <v>193.192</v>
+        <v>196.308</v>
       </c>
       <c r="G64">
         <v>25</v>
@@ -6529,37 +6529,37 @@
         <v>12.35</v>
       </c>
       <c r="M64">
-        <v>45.5546736</v>
+        <v>46.2894264</v>
       </c>
       <c r="N64">
-        <v>-33.2046736</v>
+        <v>-33.9394264</v>
       </c>
       <c r="O64">
-        <v>-11.62163576</v>
+        <v>-11.87879924</v>
       </c>
       <c r="P64">
-        <v>-21.58303784</v>
+        <v>-22.06062716</v>
       </c>
       <c r="Q64">
-        <v>-15.73303784</v>
+        <v>-16.21062716</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1780093461692509</v>
+        <v>0.1815825717413928</v>
       </c>
       <c r="T64">
-        <v>1.923807078951444</v>
+        <v>1.97580186486905</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09488598333410075</v>
+        <v>0.09337985661451184</v>
       </c>
       <c r="W64">
-        <v>0.2134258851298191</v>
+        <v>0.2137810298102981</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2711028095260022</v>
+        <v>0.2667995903271767</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2018676003248032</v>
+        <v>0.2037676003248031</v>
       </c>
       <c r="C65">
-        <v>-89.39034118213381</v>
+        <v>-93.49162899706496</v>
       </c>
       <c r="D65">
-        <v>81.91765881786621</v>
+        <v>80.93237100293504</v>
       </c>
       <c r="E65">
-        <v>9.807999999999993</v>
+        <v>12.92399999999998</v>
       </c>
       <c r="F65">
-        <v>196.308</v>
+        <v>199.424</v>
       </c>
       <c r="G65">
         <v>25</v>
@@ -6611,37 +6611,37 @@
         <v>12.35</v>
       </c>
       <c r="M65">
-        <v>46.2894264</v>
+        <v>47.02417920000001</v>
       </c>
       <c r="N65">
-        <v>-33.9394264</v>
+        <v>-34.6741792</v>
       </c>
       <c r="O65">
-        <v>-11.87879924</v>
+        <v>-12.13596272</v>
       </c>
       <c r="P65">
-        <v>-22.06062716</v>
+        <v>-22.53821648</v>
       </c>
       <c r="Q65">
-        <v>-16.21062716</v>
+        <v>-16.68821648</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1815825717413928</v>
+        <v>0.1853543098453204</v>
       </c>
       <c r="T65">
-        <v>1.97580186486905</v>
+        <v>2.030685250004301</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09337985661451184</v>
+        <v>0.09192079635491009</v>
       </c>
       <c r="W65">
-        <v>0.2137810298102981</v>
+        <v>0.2141250762195122</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2667995903271767</v>
+        <v>0.2626308467283146</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2037676003248031</v>
+        <v>0.2056676003248031</v>
       </c>
       <c r="C66">
-        <v>-93.49162899706496</v>
+        <v>-97.56949684641756</v>
       </c>
       <c r="D66">
-        <v>80.93237100293504</v>
+        <v>79.97050315358246</v>
       </c>
       <c r="E66">
-        <v>12.92399999999998</v>
+        <v>16.03999999999999</v>
       </c>
       <c r="F66">
-        <v>199.424</v>
+        <v>202.54</v>
       </c>
       <c r="G66">
         <v>25</v>
@@ -6693,37 +6693,37 @@
         <v>12.35</v>
       </c>
       <c r="M66">
-        <v>47.02417920000001</v>
+        <v>47.75893200000001</v>
       </c>
       <c r="N66">
-        <v>-34.6741792</v>
+        <v>-35.40893200000001</v>
       </c>
       <c r="O66">
-        <v>-12.13596272</v>
+        <v>-12.3931262</v>
       </c>
       <c r="P66">
-        <v>-22.53821648</v>
+        <v>-23.01580580000001</v>
       </c>
       <c r="Q66">
-        <v>-16.68821648</v>
+        <v>-17.16580580000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1853543098453204</v>
+        <v>0.189341575840901</v>
       </c>
       <c r="T66">
-        <v>2.030685250004301</v>
+        <v>2.088704828575853</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09192079635491009</v>
+        <v>0.09050663025714224</v>
       </c>
       <c r="W66">
-        <v>0.2141250762195122</v>
+        <v>0.2144585365853659</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2626308467283146</v>
+        <v>0.2585903721632636</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2056676003248031</v>
+        <v>0.2075676003248032</v>
       </c>
       <c r="C67">
-        <v>-97.56949684641756</v>
+        <v>-101.6247699498495</v>
       </c>
       <c r="D67">
-        <v>79.97050315358246</v>
+        <v>79.03123005015054</v>
       </c>
       <c r="E67">
-        <v>16.03999999999999</v>
+        <v>19.15600000000001</v>
       </c>
       <c r="F67">
-        <v>202.54</v>
+        <v>205.656</v>
       </c>
       <c r="G67">
         <v>25</v>
@@ -6775,37 +6775,37 @@
         <v>12.35</v>
       </c>
       <c r="M67">
-        <v>47.75893200000001</v>
+        <v>48.49368480000001</v>
       </c>
       <c r="N67">
-        <v>-35.40893200000001</v>
+        <v>-36.14368480000001</v>
       </c>
       <c r="O67">
-        <v>-12.3931262</v>
+        <v>-12.65028968</v>
       </c>
       <c r="P67">
-        <v>-23.01580580000001</v>
+        <v>-23.49339512000001</v>
       </c>
       <c r="Q67">
-        <v>-17.16580580000001</v>
+        <v>-17.64339512000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.189341575840901</v>
+        <v>0.1935633868950452</v>
       </c>
       <c r="T67">
-        <v>2.088704828575853</v>
+        <v>2.150137323533967</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09050663025714224</v>
+        <v>0.08913531767748856</v>
       </c>
       <c r="W67">
-        <v>0.2144585365853659</v>
+        <v>0.2147818920916482</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2585903721632636</v>
+        <v>0.254672336221396</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2075676003248032</v>
+        <v>0.2094676003248032</v>
       </c>
       <c r="C68">
-        <v>-101.6247699498495</v>
+        <v>-105.6582352074648</v>
       </c>
       <c r="D68">
-        <v>79.03123005015054</v>
+        <v>78.11376479253521</v>
       </c>
       <c r="E68">
-        <v>19.15600000000001</v>
+        <v>22.27199999999999</v>
       </c>
       <c r="F68">
-        <v>205.656</v>
+        <v>208.772</v>
       </c>
       <c r="G68">
         <v>25</v>
@@ -6857,37 +6857,37 @@
         <v>12.35</v>
       </c>
       <c r="M68">
-        <v>48.49368480000001</v>
+        <v>49.22843760000001</v>
       </c>
       <c r="N68">
-        <v>-36.14368480000001</v>
+        <v>-36.87843760000001</v>
       </c>
       <c r="O68">
-        <v>-12.65028968</v>
+        <v>-12.90745316</v>
       </c>
       <c r="P68">
-        <v>-23.49339512000001</v>
+        <v>-23.97098444</v>
       </c>
       <c r="Q68">
-        <v>-17.64339512000001</v>
+        <v>-18.12098444</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1935633868950452</v>
+        <v>0.1980410652858041</v>
       </c>
       <c r="T68">
-        <v>2.150137323533967</v>
+        <v>2.215293000004693</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08913531767748856</v>
+        <v>0.08780493980170517</v>
       </c>
       <c r="W68">
-        <v>0.2147818920916482</v>
+        <v>0.2150955951947579</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.254672336221396</v>
+        <v>0.2508712565763005</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2094676003248032</v>
+        <v>0.2113676003248031</v>
       </c>
       <c r="C69">
-        <v>-105.6582352074648</v>
+        <v>-109.670643398528</v>
       </c>
       <c r="D69">
-        <v>78.11376479253521</v>
+        <v>77.21735660147208</v>
       </c>
       <c r="E69">
-        <v>22.27199999999999</v>
+        <v>25.38800000000001</v>
       </c>
       <c r="F69">
-        <v>208.772</v>
+        <v>211.888</v>
       </c>
       <c r="G69">
         <v>25</v>
@@ -6939,37 +6939,37 @@
         <v>12.35</v>
       </c>
       <c r="M69">
-        <v>49.22843760000001</v>
+        <v>49.96319040000001</v>
       </c>
       <c r="N69">
-        <v>-36.87843760000001</v>
+        <v>-37.61319040000001</v>
       </c>
       <c r="O69">
-        <v>-12.90745316</v>
+        <v>-13.16461664</v>
       </c>
       <c r="P69">
-        <v>-23.97098444</v>
+        <v>-24.44857376000001</v>
       </c>
       <c r="Q69">
-        <v>-18.12098444</v>
+        <v>-18.59857376000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1980410652858041</v>
+        <v>0.2027985985759855</v>
       </c>
       <c r="T69">
-        <v>2.215293000004693</v>
+        <v>2.284520906254839</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08780493980170517</v>
+        <v>0.0865136906869742</v>
       </c>
       <c r="W69">
-        <v>0.2150955951947579</v>
+        <v>0.2154000717360115</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2508712565763005</v>
+        <v>0.2471819733913549</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2113676003248031</v>
+        <v>0.2132676003248032</v>
       </c>
       <c r="C70">
-        <v>-109.670643398528</v>
+        <v>-113.6627112305041</v>
       </c>
       <c r="D70">
-        <v>77.21735660147208</v>
+        <v>76.34128876949595</v>
       </c>
       <c r="E70">
-        <v>25.38800000000001</v>
+        <v>28.50400000000002</v>
       </c>
       <c r="F70">
-        <v>211.888</v>
+        <v>215.004</v>
       </c>
       <c r="G70">
         <v>25</v>
@@ -7021,37 +7021,37 @@
         <v>12.35</v>
       </c>
       <c r="M70">
-        <v>49.96319040000001</v>
+        <v>50.69794320000001</v>
       </c>
       <c r="N70">
-        <v>-37.61319040000001</v>
+        <v>-38.34794320000001</v>
       </c>
       <c r="O70">
-        <v>-13.16461664</v>
+        <v>-13.42178012</v>
       </c>
       <c r="P70">
-        <v>-24.44857376000001</v>
+        <v>-24.92616308000001</v>
       </c>
       <c r="Q70">
-        <v>-18.59857376000001</v>
+        <v>-19.07616308000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2027985985759855</v>
+        <v>0.2078630694977915</v>
       </c>
       <c r="T70">
-        <v>2.284520906254839</v>
+        <v>2.358215129037254</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0865136906869742</v>
+        <v>0.08525986908281516</v>
       </c>
       <c r="W70">
-        <v>0.2154000717360115</v>
+        <v>0.2156957228702722</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2471819733913549</v>
+        <v>0.2435996259509005</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2132676003248032</v>
+        <v>0.2151676003248031</v>
       </c>
       <c r="C71">
-        <v>-113.6627112305041</v>
+        <v>-117.6351232501813</v>
       </c>
       <c r="D71">
-        <v>76.34128876949595</v>
+        <v>75.48487674981878</v>
       </c>
       <c r="E71">
-        <v>28.50400000000002</v>
+        <v>31.62</v>
       </c>
       <c r="F71">
-        <v>215.004</v>
+        <v>218.12</v>
       </c>
       <c r="G71">
         <v>25</v>
@@ -7103,37 +7103,37 @@
         <v>12.35</v>
       </c>
       <c r="M71">
-        <v>50.69794320000001</v>
+        <v>51.43269600000001</v>
       </c>
       <c r="N71">
-        <v>-38.34794320000001</v>
+        <v>-39.08269600000001</v>
       </c>
       <c r="O71">
-        <v>-13.42178012</v>
+        <v>-13.6789436</v>
       </c>
       <c r="P71">
-        <v>-24.92616308000001</v>
+        <v>-25.4037524</v>
       </c>
       <c r="Q71">
-        <v>-19.07616308000001</v>
+        <v>-19.5537524</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2078630694977915</v>
+        <v>0.2132651718143845</v>
       </c>
       <c r="T71">
-        <v>2.358215129037254</v>
+        <v>2.436822300005162</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08525986908281516</v>
+        <v>0.08404187095306066</v>
       </c>
       <c r="W71">
-        <v>0.2156957228702722</v>
+        <v>0.2159829268292683</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2435996259509005</v>
+        <v>0.240119631294459</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2151676003248031</v>
+        <v>0.2170676003248032</v>
       </c>
       <c r="C72">
-        <v>-117.6351232501813</v>
+        <v>-121.5885336275829</v>
       </c>
       <c r="D72">
-        <v>75.48487674981878</v>
+        <v>74.64746637241717</v>
       </c>
       <c r="E72">
-        <v>31.62</v>
+        <v>34.73600000000002</v>
       </c>
       <c r="F72">
-        <v>218.12</v>
+        <v>221.236</v>
       </c>
       <c r="G72">
         <v>25</v>
@@ -7185,37 +7185,37 @@
         <v>12.35</v>
       </c>
       <c r="M72">
-        <v>51.43269600000001</v>
+        <v>52.16744880000002</v>
       </c>
       <c r="N72">
-        <v>-39.08269600000001</v>
+        <v>-39.81744880000002</v>
       </c>
       <c r="O72">
-        <v>-13.6789436</v>
+        <v>-13.93610708</v>
       </c>
       <c r="P72">
-        <v>-25.4037524</v>
+        <v>-25.88134172000001</v>
       </c>
       <c r="Q72">
-        <v>-19.5537524</v>
+        <v>-20.03134172000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2132651718143845</v>
+        <v>0.2190398329114323</v>
       </c>
       <c r="T72">
-        <v>2.436822300005162</v>
+        <v>2.520850655177755</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08404187095306066</v>
+        <v>0.08285818262977809</v>
       </c>
       <c r="W72">
-        <v>0.2159829268292683</v>
+        <v>0.2162620405358983</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.240119631294459</v>
+        <v>0.2367376646565089</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2170676003248032</v>
+        <v>0.2189676003248032</v>
       </c>
       <c r="C73">
-        <v>-121.5885336275828</v>
+        <v>-125.5235678224412</v>
       </c>
       <c r="D73">
-        <v>74.64746637241723</v>
+        <v>73.82843217755878</v>
       </c>
       <c r="E73">
-        <v>34.73599999999999</v>
+        <v>37.85199999999998</v>
       </c>
       <c r="F73">
-        <v>221.236</v>
+        <v>224.352</v>
       </c>
       <c r="G73">
         <v>25</v>
@@ -7267,37 +7267,37 @@
         <v>12.35</v>
       </c>
       <c r="M73">
-        <v>52.16744880000001</v>
+        <v>52.90220160000001</v>
       </c>
       <c r="N73">
-        <v>-39.81744880000001</v>
+        <v>-40.5522016</v>
       </c>
       <c r="O73">
-        <v>-13.93610708</v>
+        <v>-14.19327056</v>
       </c>
       <c r="P73">
-        <v>-25.88134172000001</v>
+        <v>-26.35893104</v>
       </c>
       <c r="Q73">
-        <v>-20.03134172000001</v>
+        <v>-20.50893104</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2190398329114322</v>
+        <v>0.2252269698011262</v>
       </c>
       <c r="T73">
-        <v>2.520850655177754</v>
+        <v>2.610881035719816</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08285818262977811</v>
+        <v>0.08170737453769786</v>
       </c>
       <c r="W73">
-        <v>0.2162620405358983</v>
+        <v>0.2165334010840109</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2367376646565089</v>
+        <v>0.2334496415362797</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2189676003248032</v>
+        <v>0.2208676003248032</v>
       </c>
       <c r="C74">
-        <v>-125.5235678224412</v>
+        <v>-129.440824142155</v>
       </c>
       <c r="D74">
-        <v>73.82843217755878</v>
+        <v>73.02717585784502</v>
       </c>
       <c r="E74">
-        <v>37.85199999999998</v>
+        <v>40.96799999999999</v>
       </c>
       <c r="F74">
-        <v>224.352</v>
+        <v>227.468</v>
       </c>
       <c r="G74">
         <v>25</v>
@@ -7349,37 +7349,37 @@
         <v>12.35</v>
       </c>
       <c r="M74">
-        <v>52.90220160000001</v>
+        <v>53.63695440000001</v>
       </c>
       <c r="N74">
-        <v>-40.5522016</v>
+        <v>-41.28695440000001</v>
       </c>
       <c r="O74">
-        <v>-14.19327056</v>
+        <v>-14.45043404</v>
       </c>
       <c r="P74">
-        <v>-26.35893104</v>
+        <v>-26.83652036000001</v>
       </c>
       <c r="Q74">
-        <v>-20.50893104</v>
+        <v>-20.98652036000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2252269698011262</v>
+        <v>0.2318724131270939</v>
       </c>
       <c r="T74">
-        <v>2.610881035719816</v>
+        <v>2.707580333339068</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08170737453769786</v>
+        <v>0.08058809543444173</v>
       </c>
       <c r="W74">
-        <v>0.2165334010840109</v>
+        <v>0.2167973270965586</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2334496415362797</v>
+        <v>0.2302517012412622</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2208676003248032</v>
+        <v>0.2227676003248031</v>
       </c>
       <c r="C75">
-        <v>-129.440824142155</v>
+        <v>-133.3408751993837</v>
       </c>
       <c r="D75">
-        <v>73.02717585784502</v>
+        <v>72.2431248006163</v>
       </c>
       <c r="E75">
-        <v>40.96799999999999</v>
+        <v>44.08399999999997</v>
       </c>
       <c r="F75">
-        <v>227.468</v>
+        <v>230.584</v>
       </c>
       <c r="G75">
         <v>25</v>
@@ -7431,37 +7431,37 @@
         <v>12.35</v>
       </c>
       <c r="M75">
-        <v>53.63695440000001</v>
+        <v>54.3717072</v>
       </c>
       <c r="N75">
-        <v>-41.28695440000001</v>
+        <v>-42.0217072</v>
       </c>
       <c r="O75">
-        <v>-14.45043404</v>
+        <v>-14.70759752</v>
       </c>
       <c r="P75">
-        <v>-26.83652036000001</v>
+        <v>-27.31410968</v>
       </c>
       <c r="Q75">
-        <v>-20.98652036000001</v>
+        <v>-21.46410968</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2318724131270939</v>
+        <v>0.2390290444012129</v>
       </c>
       <c r="T75">
-        <v>2.707580333339068</v>
+        <v>2.811718038467494</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08058809543444173</v>
+        <v>0.07949906711776009</v>
       </c>
       <c r="W75">
-        <v>0.2167973270965586</v>
+        <v>0.2170541199736322</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2302517012412622</v>
+        <v>0.2271401917650289</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2227676003248031</v>
+        <v>0.2246676003248032</v>
       </c>
       <c r="C76">
-        <v>-133.3408751993837</v>
+        <v>-137.2242692767456</v>
       </c>
       <c r="D76">
-        <v>72.2431248006163</v>
+        <v>71.47573072325444</v>
       </c>
       <c r="E76">
-        <v>44.08399999999997</v>
+        <v>47.19999999999999</v>
       </c>
       <c r="F76">
-        <v>230.584</v>
+        <v>233.7</v>
       </c>
       <c r="G76">
         <v>25</v>
@@ -7513,37 +7513,37 @@
         <v>12.35</v>
       </c>
       <c r="M76">
-        <v>54.3717072</v>
+        <v>55.10646000000001</v>
       </c>
       <c r="N76">
-        <v>-42.0217072</v>
+        <v>-42.75646</v>
       </c>
       <c r="O76">
-        <v>-14.70759752</v>
+        <v>-14.964761</v>
       </c>
       <c r="P76">
-        <v>-27.31410968</v>
+        <v>-27.791699</v>
       </c>
       <c r="Q76">
-        <v>-21.46410968</v>
+        <v>-21.941699</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2390290444012129</v>
+        <v>0.2467582061772614</v>
       </c>
       <c r="T76">
-        <v>2.811718038467494</v>
+        <v>2.924186760006194</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07949906711776009</v>
+        <v>0.07843907955618995</v>
       </c>
       <c r="W76">
-        <v>0.2170541199736322</v>
+        <v>0.2173040650406504</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2271401917650289</v>
+        <v>0.2241116558748285</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2246676003248032</v>
+        <v>0.2265676003248032</v>
       </c>
       <c r="C77">
-        <v>-137.2242692767456</v>
+        <v>-141.0915316054492</v>
       </c>
       <c r="D77">
-        <v>71.47573072325444</v>
+        <v>70.72446839455081</v>
       </c>
       <c r="E77">
-        <v>47.19999999999999</v>
+        <v>50.316</v>
       </c>
       <c r="F77">
-        <v>233.7</v>
+        <v>236.816</v>
       </c>
       <c r="G77">
         <v>25</v>
@@ -7595,37 +7595,37 @@
         <v>12.35</v>
       </c>
       <c r="M77">
-        <v>55.10646000000001</v>
+        <v>55.84121280000001</v>
       </c>
       <c r="N77">
-        <v>-42.75646</v>
+        <v>-43.49121280000001</v>
       </c>
       <c r="O77">
-        <v>-14.964761</v>
+        <v>-15.22192448</v>
       </c>
       <c r="P77">
-        <v>-27.791699</v>
+        <v>-28.26928832</v>
       </c>
       <c r="Q77">
-        <v>-21.941699</v>
+        <v>-22.41928832000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2467582061772614</v>
+        <v>0.2551314647679807</v>
       </c>
       <c r="T77">
-        <v>2.924186760006194</v>
+        <v>3.046027875006453</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07843907955618995</v>
+        <v>0.07740698640413482</v>
       </c>
       <c r="W77">
-        <v>0.2173040650406504</v>
+        <v>0.217547432605905</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2241116558748285</v>
+        <v>0.221162818297528</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2265676003248032</v>
+        <v>0.2284676003248031</v>
       </c>
       <c r="C78">
-        <v>-141.0915316054492</v>
+        <v>-144.9431655641299</v>
       </c>
       <c r="D78">
-        <v>70.72446839455081</v>
+        <v>69.9888344358701</v>
       </c>
       <c r="E78">
-        <v>50.316</v>
+        <v>53.43199999999999</v>
       </c>
       <c r="F78">
-        <v>236.816</v>
+        <v>239.932</v>
       </c>
       <c r="G78">
         <v>25</v>
@@ -7677,37 +7677,37 @@
         <v>12.35</v>
       </c>
       <c r="M78">
-        <v>55.84121280000001</v>
+        <v>56.5759656</v>
       </c>
       <c r="N78">
-        <v>-43.49121280000001</v>
+        <v>-44.2259656</v>
       </c>
       <c r="O78">
-        <v>-15.22192448</v>
+        <v>-15.47908796</v>
       </c>
       <c r="P78">
-        <v>-28.26928832</v>
+        <v>-28.74687764</v>
       </c>
       <c r="Q78">
-        <v>-22.41928832000001</v>
+        <v>-22.89687764</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2551314647679807</v>
+        <v>0.2642328328013711</v>
       </c>
       <c r="T78">
-        <v>3.046027875006453</v>
+        <v>3.17846386957195</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07740698640413482</v>
+        <v>0.07640170086641879</v>
       </c>
       <c r="W78">
-        <v>0.217547432605905</v>
+        <v>0.2177844789356984</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.221162818297528</v>
+        <v>0.2182905739040537</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2284676003248031</v>
+        <v>0.2303676003248032</v>
       </c>
       <c r="C79">
-        <v>-144.9431655641299</v>
+        <v>-148.7796538036375</v>
       </c>
       <c r="D79">
-        <v>69.9888344358701</v>
+        <v>69.26834619636249</v>
       </c>
       <c r="E79">
-        <v>53.43199999999999</v>
+        <v>56.548</v>
       </c>
       <c r="F79">
-        <v>239.932</v>
+        <v>243.048</v>
       </c>
       <c r="G79">
         <v>25</v>
@@ -7759,37 +7759,37 @@
         <v>12.35</v>
       </c>
       <c r="M79">
-        <v>56.5759656</v>
+        <v>57.31071840000001</v>
       </c>
       <c r="N79">
-        <v>-44.2259656</v>
+        <v>-44.9607184</v>
       </c>
       <c r="O79">
-        <v>-15.47908796</v>
+        <v>-15.73625144</v>
       </c>
       <c r="P79">
-        <v>-28.74687764</v>
+        <v>-29.22446696</v>
       </c>
       <c r="Q79">
-        <v>-22.89687764</v>
+        <v>-23.37446696000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2642328328013711</v>
+        <v>0.2741615979287061</v>
       </c>
       <c r="T79">
-        <v>3.17846386957195</v>
+        <v>3.322939500007039</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07640170086641879</v>
+        <v>0.07542219188095187</v>
       </c>
       <c r="W79">
-        <v>0.2177844789356984</v>
+        <v>0.2180154471544715</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2182905739040537</v>
+        <v>0.2154919768027197</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2303676003248032</v>
+        <v>0.2322676003248032</v>
       </c>
       <c r="C80">
-        <v>-148.7796538036375</v>
+        <v>-152.6014593030586</v>
       </c>
       <c r="D80">
-        <v>69.26834619636249</v>
+        <v>68.56254069694145</v>
       </c>
       <c r="E80">
-        <v>56.548</v>
+        <v>59.66399999999999</v>
       </c>
       <c r="F80">
-        <v>243.048</v>
+        <v>246.164</v>
       </c>
       <c r="G80">
         <v>25</v>
@@ -7841,37 +7841,37 @@
         <v>12.35</v>
       </c>
       <c r="M80">
-        <v>57.31071840000001</v>
+        <v>58.04547120000001</v>
       </c>
       <c r="N80">
-        <v>-44.9607184</v>
+        <v>-45.69547120000001</v>
       </c>
       <c r="O80">
-        <v>-15.73625144</v>
+        <v>-15.99341492</v>
       </c>
       <c r="P80">
-        <v>-29.22446696</v>
+        <v>-29.70205628000001</v>
       </c>
       <c r="Q80">
-        <v>-23.37446696000001</v>
+        <v>-23.85205628000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2741615979287061</v>
+        <v>0.285035959734835</v>
       </c>
       <c r="T80">
-        <v>3.322939500007039</v>
+        <v>3.481174714293089</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07542219188095187</v>
+        <v>0.07446748059131957</v>
       </c>
       <c r="W80">
-        <v>0.2180154471544715</v>
+        <v>0.2182405680765669</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2154919768027197</v>
+        <v>0.2127642302609131</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2322676003248032</v>
+        <v>0.2341676003248032</v>
       </c>
       <c r="C81">
-        <v>-152.6014593030586</v>
+        <v>-156.4090263618286</v>
       </c>
       <c r="D81">
-        <v>68.56254069694145</v>
+        <v>67.87097363817148</v>
       </c>
       <c r="E81">
-        <v>59.66399999999999</v>
+        <v>62.78</v>
       </c>
       <c r="F81">
-        <v>246.164</v>
+        <v>249.28</v>
       </c>
       <c r="G81">
         <v>25</v>
@@ -7923,37 +7923,37 @@
         <v>12.35</v>
       </c>
       <c r="M81">
-        <v>58.04547120000001</v>
+        <v>58.78022400000001</v>
       </c>
       <c r="N81">
-        <v>-45.69547120000001</v>
+        <v>-46.43022400000001</v>
       </c>
       <c r="O81">
-        <v>-15.99341492</v>
+        <v>-16.2505784</v>
       </c>
       <c r="P81">
-        <v>-29.70205628000001</v>
+        <v>-30.17964560000001</v>
       </c>
       <c r="Q81">
-        <v>-23.85205628000001</v>
+        <v>-24.32964560000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.285035959734835</v>
+        <v>0.2969977577215768</v>
       </c>
       <c r="T81">
-        <v>3.481174714293089</v>
+        <v>3.655233450007743</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07446748059131957</v>
+        <v>0.07353663708392807</v>
       </c>
       <c r="W81">
-        <v>0.2182405680765669</v>
+        <v>0.2184600609756098</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2127642302609131</v>
+        <v>0.2101046773826517</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2341676003248032</v>
+        <v>0.2360676003248032</v>
       </c>
       <c r="C82">
-        <v>-156.4090263618286</v>
+        <v>-160.2027815324009</v>
       </c>
       <c r="D82">
-        <v>67.87097363817148</v>
+        <v>67.19321846759912</v>
       </c>
       <c r="E82">
-        <v>62.78</v>
+        <v>65.89600000000002</v>
       </c>
       <c r="F82">
-        <v>249.28</v>
+        <v>252.396</v>
       </c>
       <c r="G82">
         <v>25</v>
@@ -8005,37 +8005,37 @@
         <v>12.35</v>
       </c>
       <c r="M82">
-        <v>58.78022400000001</v>
+        <v>59.51497680000001</v>
       </c>
       <c r="N82">
-        <v>-46.43022400000001</v>
+        <v>-47.16497680000001</v>
       </c>
       <c r="O82">
-        <v>-16.2505784</v>
+        <v>-16.50774188</v>
       </c>
       <c r="P82">
-        <v>-30.17964560000001</v>
+        <v>-30.65723492000001</v>
       </c>
       <c r="Q82">
-        <v>-24.32964560000001</v>
+        <v>-24.80723492000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2969977577215768</v>
+        <v>0.3102186923385019</v>
       </c>
       <c r="T82">
-        <v>3.655233450007743</v>
+        <v>3.847614157902888</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07353663708392807</v>
+        <v>0.07262877736684253</v>
       </c>
       <c r="W82">
-        <v>0.2184600609756098</v>
+        <v>0.2186741342968985</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2101046773826517</v>
+        <v>0.207510792476693</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2360676003248032</v>
+        <v>0.2379676003248032</v>
       </c>
       <c r="C83">
-        <v>-160.2027815324009</v>
+        <v>-163.9831344975868</v>
       </c>
       <c r="D83">
-        <v>67.19321846759912</v>
+        <v>66.52886550241321</v>
       </c>
       <c r="E83">
-        <v>65.89600000000002</v>
+        <v>69.012</v>
       </c>
       <c r="F83">
-        <v>252.396</v>
+        <v>255.512</v>
       </c>
       <c r="G83">
         <v>25</v>
@@ -8087,37 +8087,37 @@
         <v>12.35</v>
       </c>
       <c r="M83">
-        <v>59.51497680000001</v>
+        <v>60.24972960000001</v>
       </c>
       <c r="N83">
-        <v>-47.16497680000001</v>
+        <v>-47.89972960000001</v>
       </c>
       <c r="O83">
-        <v>-16.50774188</v>
+        <v>-16.76490536</v>
       </c>
       <c r="P83">
-        <v>-30.65723492000001</v>
+        <v>-31.13482424000001</v>
       </c>
       <c r="Q83">
-        <v>-24.80723492000001</v>
+        <v>-25.28482424000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3102186923385019</v>
+        <v>0.3249086196906409</v>
       </c>
       <c r="T83">
-        <v>3.847614157902888</v>
+        <v>4.061370500008604</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07262877736684253</v>
+        <v>0.07174306056968593</v>
       </c>
       <c r="W83">
-        <v>0.2186741342968985</v>
+        <v>0.2188829863176681</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.207510792476693</v>
+        <v>0.2049801730562455</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2379676003248032</v>
+        <v>0.2398676003248032</v>
       </c>
       <c r="C84">
-        <v>-163.9831344975868</v>
+        <v>-167.7504788963583</v>
       </c>
       <c r="D84">
-        <v>66.52886550241321</v>
+        <v>65.87752110364175</v>
       </c>
       <c r="E84">
-        <v>69.012</v>
+        <v>72.12800000000001</v>
       </c>
       <c r="F84">
-        <v>255.512</v>
+        <v>258.628</v>
       </c>
       <c r="G84">
         <v>25</v>
@@ -8169,37 +8169,37 @@
         <v>12.35</v>
       </c>
       <c r="M84">
-        <v>60.24972960000001</v>
+        <v>60.98448240000001</v>
       </c>
       <c r="N84">
-        <v>-47.89972960000001</v>
+        <v>-48.63448240000001</v>
       </c>
       <c r="O84">
-        <v>-16.76490536</v>
+        <v>-17.02206884</v>
       </c>
       <c r="P84">
-        <v>-31.13482424000001</v>
+        <v>-31.61241356000001</v>
       </c>
       <c r="Q84">
-        <v>-25.28482424000001</v>
+        <v>-25.76241356000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3249086196906409</v>
+        <v>0.3413267737900905</v>
       </c>
       <c r="T84">
-        <v>4.061370500008604</v>
+        <v>4.300274647067935</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07174306056968593</v>
+        <v>0.07087868634595478</v>
       </c>
       <c r="W84">
-        <v>0.2188829863176681</v>
+        <v>0.2190868057596239</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2049801730562455</v>
+        <v>0.2025105324170137</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2398676003248032</v>
+        <v>0.2417676003248032</v>
       </c>
       <c r="C85">
-        <v>-167.7504788963583</v>
+        <v>-171.5051931016119</v>
       </c>
       <c r="D85">
-        <v>65.87752110364175</v>
+        <v>65.23880689838811</v>
       </c>
       <c r="E85">
-        <v>72.12800000000001</v>
+        <v>75.244</v>
       </c>
       <c r="F85">
-        <v>258.628</v>
+        <v>261.744</v>
       </c>
       <c r="G85">
         <v>25</v>
@@ -8251,37 +8251,37 @@
         <v>12.35</v>
       </c>
       <c r="M85">
-        <v>60.98448240000001</v>
+        <v>61.71923520000001</v>
       </c>
       <c r="N85">
-        <v>-48.63448240000001</v>
+        <v>-49.36923520000001</v>
       </c>
       <c r="O85">
-        <v>-17.02206884</v>
+        <v>-17.27923232</v>
       </c>
       <c r="P85">
-        <v>-31.61241356000001</v>
+        <v>-32.09000288</v>
       </c>
       <c r="Q85">
-        <v>-25.76241356000001</v>
+        <v>-26.24000288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3413267737900905</v>
+        <v>0.3597971971519711</v>
       </c>
       <c r="T85">
-        <v>4.300274647067935</v>
+        <v>4.569041812509681</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07087868634595478</v>
+        <v>0.07003489246088387</v>
       </c>
       <c r="W85">
-        <v>0.2190868057596239</v>
+        <v>0.2192857723577236</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2025105324170137</v>
+        <v>0.2000996927453825</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2417676003248032</v>
+        <v>0.2436676003248031</v>
       </c>
       <c r="C86">
-        <v>-171.505193101612</v>
+        <v>-175.2476409531221</v>
       </c>
       <c r="D86">
-        <v>65.23880689838806</v>
+        <v>64.61235904687796</v>
       </c>
       <c r="E86">
-        <v>75.244</v>
+        <v>78.35999999999999</v>
       </c>
       <c r="F86">
-        <v>261.744</v>
+        <v>264.86</v>
       </c>
       <c r="G86">
         <v>25</v>
@@ -8333,37 +8333,37 @@
         <v>12.35</v>
       </c>
       <c r="M86">
-        <v>61.71923520000001</v>
+        <v>62.453988</v>
       </c>
       <c r="N86">
-        <v>-49.36923520000001</v>
+        <v>-50.103988</v>
       </c>
       <c r="O86">
-        <v>-17.27923232</v>
+        <v>-17.5363958</v>
       </c>
       <c r="P86">
-        <v>-32.09000288</v>
+        <v>-32.56759220000001</v>
       </c>
       <c r="Q86">
-        <v>-26.24000288</v>
+        <v>-26.71759220000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3597971971519709</v>
+        <v>0.3807303436287689</v>
       </c>
       <c r="T86">
-        <v>4.569041812509679</v>
+        <v>4.873644600010323</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07003489246088387</v>
+        <v>0.06921095254957937</v>
       </c>
       <c r="W86">
-        <v>0.2192857723577236</v>
+        <v>0.2194800573888092</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2000996927453825</v>
+        <v>0.197745578713084</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2436676003248031</v>
+        <v>0.2455676003248032</v>
       </c>
       <c r="C87">
-        <v>-175.2476409531221</v>
+        <v>-178.9781724486672</v>
       </c>
       <c r="D87">
-        <v>64.61235904687796</v>
+        <v>63.99782755133281</v>
       </c>
       <c r="E87">
-        <v>78.35999999999999</v>
+        <v>81.47599999999997</v>
       </c>
       <c r="F87">
-        <v>264.86</v>
+        <v>267.976</v>
       </c>
       <c r="G87">
         <v>25</v>
@@ -8415,37 +8415,37 @@
         <v>12.35</v>
       </c>
       <c r="M87">
-        <v>62.453988</v>
+        <v>63.18874080000001</v>
       </c>
       <c r="N87">
-        <v>-50.103988</v>
+        <v>-50.8387408</v>
       </c>
       <c r="O87">
-        <v>-17.5363958</v>
+        <v>-17.79355928</v>
       </c>
       <c r="P87">
-        <v>-32.56759220000001</v>
+        <v>-33.04518152</v>
       </c>
       <c r="Q87">
-        <v>-26.71759220000001</v>
+        <v>-27.19518152</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3807303436287689</v>
+        <v>0.4046539396022524</v>
       </c>
       <c r="T87">
-        <v>4.873644600010323</v>
+        <v>5.221762071439632</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06921095254957937</v>
+        <v>0.068406174031561</v>
       </c>
       <c r="W87">
-        <v>0.2194800573888092</v>
+        <v>0.2196698241633579</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.197745578713084</v>
+        <v>0.1954462115187457</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2455676003248032</v>
+        <v>0.2474676003248032</v>
       </c>
       <c r="C88">
-        <v>-178.9781724486672</v>
+        <v>-182.6971243960881</v>
       </c>
       <c r="D88">
-        <v>63.99782755133281</v>
+        <v>63.39487560391196</v>
       </c>
       <c r="E88">
-        <v>81.47599999999997</v>
+        <v>84.59200000000001</v>
       </c>
       <c r="F88">
-        <v>267.976</v>
+        <v>271.092</v>
       </c>
       <c r="G88">
         <v>25</v>
@@ -8497,37 +8497,37 @@
         <v>12.35</v>
       </c>
       <c r="M88">
-        <v>63.18874080000001</v>
+        <v>63.92349360000001</v>
       </c>
       <c r="N88">
-        <v>-50.8387408</v>
+        <v>-51.57349360000001</v>
       </c>
       <c r="O88">
-        <v>-17.79355928</v>
+        <v>-18.05072276</v>
       </c>
       <c r="P88">
-        <v>-33.04518152</v>
+        <v>-33.52277084000001</v>
       </c>
       <c r="Q88">
-        <v>-27.19518152</v>
+        <v>-27.67277084000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4046539396022524</v>
+        <v>0.4322580888024257</v>
       </c>
       <c r="T88">
-        <v>5.221762071439632</v>
+        <v>5.623436076934989</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.068406174031561</v>
+        <v>0.06761989616912925</v>
       </c>
       <c r="W88">
-        <v>0.2196698241633579</v>
+        <v>0.2198552284833193</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1954462115187457</v>
+        <v>0.1931997033403694</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2474676003248032</v>
+        <v>0.2493676003248032</v>
       </c>
       <c r="C89">
-        <v>-182.6971243960881</v>
+        <v>-186.4048210288294</v>
       </c>
       <c r="D89">
-        <v>63.39487560391196</v>
+        <v>62.8031789711706</v>
       </c>
       <c r="E89">
-        <v>84.59200000000001</v>
+        <v>87.708</v>
       </c>
       <c r="F89">
-        <v>271.092</v>
+        <v>274.208</v>
       </c>
       <c r="G89">
         <v>25</v>
@@ -8579,37 +8579,37 @@
         <v>12.35</v>
       </c>
       <c r="M89">
-        <v>63.92349360000001</v>
+        <v>64.65824640000001</v>
       </c>
       <c r="N89">
-        <v>-51.57349360000001</v>
+        <v>-52.30824640000001</v>
       </c>
       <c r="O89">
-        <v>-18.05072276</v>
+        <v>-18.30788624</v>
       </c>
       <c r="P89">
-        <v>-33.52277084000001</v>
+        <v>-34.00036016000001</v>
       </c>
       <c r="Q89">
-        <v>-27.67277084000001</v>
+        <v>-28.15036016000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4322580888024257</v>
+        <v>0.4644629295359613</v>
       </c>
       <c r="T89">
-        <v>5.623436076934989</v>
+        <v>6.092055750012905</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06761989616912925</v>
+        <v>0.06685148825811643</v>
       </c>
       <c r="W89">
-        <v>0.2198552284833193</v>
+        <v>0.2200364190687362</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1931997033403694</v>
+        <v>0.191004252166047</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2493676003248032</v>
+        <v>0.2512676003248032</v>
       </c>
       <c r="C90">
-        <v>-186.4048210288294</v>
+        <v>-190.1015745873301</v>
       </c>
       <c r="D90">
-        <v>62.8031789711706</v>
+        <v>62.22242541266987</v>
       </c>
       <c r="E90">
-        <v>87.708</v>
+        <v>90.82399999999998</v>
       </c>
       <c r="F90">
-        <v>274.208</v>
+        <v>277.324</v>
       </c>
       <c r="G90">
         <v>25</v>
@@ -8661,37 +8661,37 @@
         <v>12.35</v>
       </c>
       <c r="M90">
-        <v>64.65824640000001</v>
+        <v>65.39299920000001</v>
       </c>
       <c r="N90">
-        <v>-52.30824640000001</v>
+        <v>-53.0429992</v>
       </c>
       <c r="O90">
-        <v>-18.30788624</v>
+        <v>-18.56504972</v>
       </c>
       <c r="P90">
-        <v>-34.00036016000001</v>
+        <v>-34.47794948000001</v>
       </c>
       <c r="Q90">
-        <v>-28.15036016000001</v>
+        <v>-28.62794948000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4644629295359613</v>
+        <v>0.5025231958574123</v>
       </c>
       <c r="T90">
-        <v>6.092055750012905</v>
+        <v>6.645879000014079</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06685148825811643</v>
+        <v>0.06610034794060951</v>
       </c>
       <c r="W90">
-        <v>0.2200364190687362</v>
+        <v>0.2202135379556043</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.191004252166047</v>
+        <v>0.1888581369731701</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2512676003248032</v>
+        <v>0.2531676003248032</v>
       </c>
       <c r="C91">
-        <v>-190.1015745873301</v>
+        <v>-193.7876858684508</v>
       </c>
       <c r="D91">
-        <v>62.22242541266987</v>
+        <v>61.65231413154932</v>
       </c>
       <c r="E91">
-        <v>90.82399999999998</v>
+        <v>93.94000000000003</v>
       </c>
       <c r="F91">
-        <v>277.324</v>
+        <v>280.4400000000001</v>
       </c>
       <c r="G91">
         <v>25</v>
@@ -8743,37 +8743,37 @@
         <v>12.35</v>
       </c>
       <c r="M91">
-        <v>65.39299920000001</v>
+        <v>66.12775200000002</v>
       </c>
       <c r="N91">
-        <v>-53.0429992</v>
+        <v>-53.77775200000001</v>
       </c>
       <c r="O91">
-        <v>-18.56504972</v>
+        <v>-18.8222132</v>
       </c>
       <c r="P91">
-        <v>-34.47794948000001</v>
+        <v>-34.95553880000001</v>
       </c>
       <c r="Q91">
-        <v>-28.62794948000001</v>
+        <v>-29.10553880000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5025231958574123</v>
+        <v>0.5481955154431535</v>
       </c>
       <c r="T91">
-        <v>6.645879000014079</v>
+        <v>7.310466900015487</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06610034794060951</v>
+        <v>0.06536589963015829</v>
       </c>
       <c r="W91">
-        <v>0.2202135379556043</v>
+        <v>0.2203867208672087</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1888581369731701</v>
+        <v>0.1867597132290237</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2531676003248032</v>
+        <v>0.2550676003248031</v>
       </c>
       <c r="C92">
-        <v>-193.7876858684508</v>
+        <v>-197.4634447449712</v>
       </c>
       <c r="D92">
-        <v>61.65231413154932</v>
+        <v>61.09255525502887</v>
       </c>
       <c r="E92">
-        <v>93.94000000000003</v>
+        <v>97.05600000000001</v>
       </c>
       <c r="F92">
-        <v>280.4400000000001</v>
+        <v>283.556</v>
       </c>
       <c r="G92">
         <v>25</v>
@@ -8825,37 +8825,37 @@
         <v>12.35</v>
       </c>
       <c r="M92">
-        <v>66.12775200000002</v>
+        <v>66.86250480000001</v>
       </c>
       <c r="N92">
-        <v>-53.77775200000001</v>
+        <v>-54.51250480000001</v>
       </c>
       <c r="O92">
-        <v>-18.8222132</v>
+        <v>-19.07937668</v>
       </c>
       <c r="P92">
-        <v>-34.95553880000001</v>
+        <v>-35.43312812000001</v>
       </c>
       <c r="Q92">
-        <v>-29.10553880000001</v>
+        <v>-29.58312812</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5481955154431535</v>
+        <v>0.6040172393812817</v>
       </c>
       <c r="T92">
-        <v>7.310466900015487</v>
+        <v>8.122741000017209</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06536589963015829</v>
+        <v>0.0646475930408159</v>
       </c>
       <c r="W92">
-        <v>0.2203867208672087</v>
+        <v>0.2205560975609756</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1867597132290237</v>
+        <v>0.1847074086880455</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2550676003248031</v>
+        <v>0.2569676003248031</v>
       </c>
       <c r="C93">
-        <v>-197.4634447449712</v>
+        <v>-201.1291306570429</v>
       </c>
       <c r="D93">
-        <v>61.09255525502887</v>
+        <v>60.54286934295708</v>
       </c>
       <c r="E93">
-        <v>97.05600000000001</v>
+        <v>100.172</v>
       </c>
       <c r="F93">
-        <v>283.556</v>
+        <v>286.672</v>
       </c>
       <c r="G93">
         <v>25</v>
@@ -8907,37 +8907,37 @@
         <v>12.35</v>
       </c>
       <c r="M93">
-        <v>66.86250480000001</v>
+        <v>67.59725760000001</v>
       </c>
       <c r="N93">
-        <v>-54.51250480000001</v>
+        <v>-55.2472576</v>
       </c>
       <c r="O93">
-        <v>-19.07937668</v>
+        <v>-19.33654016</v>
       </c>
       <c r="P93">
-        <v>-35.43312812000001</v>
+        <v>-35.91071744</v>
       </c>
       <c r="Q93">
-        <v>-29.58312812</v>
+        <v>-30.06071744</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6040172393812817</v>
+        <v>0.6737943943039422</v>
       </c>
       <c r="T93">
-        <v>8.122741000017209</v>
+        <v>9.138083625019362</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0646475930408159</v>
+        <v>0.06394490181211138</v>
       </c>
       <c r="W93">
-        <v>0.2205560975609756</v>
+        <v>0.2207217921527041</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1847074086880455</v>
+        <v>0.1826997194631754</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2569676003248031</v>
+        <v>0.2588676003248032</v>
       </c>
       <c r="C94">
-        <v>-201.1291306570429</v>
+        <v>-204.7850130773465</v>
       </c>
       <c r="D94">
-        <v>60.54286934295708</v>
+        <v>60.00298692265356</v>
       </c>
       <c r="E94">
-        <v>100.172</v>
+        <v>103.288</v>
       </c>
       <c r="F94">
-        <v>286.672</v>
+        <v>289.788</v>
       </c>
       <c r="G94">
         <v>25</v>
@@ -8989,37 +8989,37 @@
         <v>12.35</v>
       </c>
       <c r="M94">
-        <v>67.59725760000001</v>
+        <v>68.3320104</v>
       </c>
       <c r="N94">
-        <v>-55.2472576</v>
+        <v>-55.9820104</v>
       </c>
       <c r="O94">
-        <v>-19.33654016</v>
+        <v>-19.59370364</v>
       </c>
       <c r="P94">
-        <v>-35.91071744</v>
+        <v>-36.38830676000001</v>
       </c>
       <c r="Q94">
-        <v>-30.06071744</v>
+        <v>-30.53830676</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6737943943039422</v>
+        <v>0.7635078792045054</v>
       </c>
       <c r="T94">
-        <v>9.138083625019362</v>
+        <v>10.44352414287927</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06394490181211138</v>
+        <v>0.06325732222273384</v>
       </c>
       <c r="W94">
-        <v>0.2207217921527041</v>
+        <v>0.2208839234198794</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1826997194631754</v>
+        <v>0.1807352063506681</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2588676003248032</v>
+        <v>0.2607676003248032</v>
       </c>
       <c r="C95">
-        <v>-204.7850130773465</v>
+        <v>-208.4313519515805</v>
       </c>
       <c r="D95">
-        <v>60.00298692265356</v>
+        <v>59.47264804841954</v>
       </c>
       <c r="E95">
-        <v>103.288</v>
+        <v>106.404</v>
       </c>
       <c r="F95">
-        <v>289.788</v>
+        <v>292.9040000000001</v>
       </c>
       <c r="G95">
         <v>25</v>
@@ -9071,37 +9071,37 @@
         <v>12.35</v>
       </c>
       <c r="M95">
-        <v>68.3320104</v>
+        <v>69.06676320000001</v>
       </c>
       <c r="N95">
-        <v>-55.9820104</v>
+        <v>-56.71676320000001</v>
       </c>
       <c r="O95">
-        <v>-19.59370364</v>
+        <v>-19.85086712</v>
       </c>
       <c r="P95">
-        <v>-36.38830676000001</v>
+        <v>-36.86589608000001</v>
       </c>
       <c r="Q95">
-        <v>-30.53830676</v>
+        <v>-31.01589608</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7635078792045054</v>
+        <v>0.8831258590719232</v>
       </c>
       <c r="T95">
-        <v>10.44352414287927</v>
+        <v>12.18411150002582</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06325732222273384</v>
+        <v>0.06258437198632176</v>
       </c>
       <c r="W95">
-        <v>0.2208839234198794</v>
+        <v>0.2210426050856253</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1807352063506681</v>
+        <v>0.1788124913894908</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2607676003248032</v>
+        <v>0.2626676003248032</v>
       </c>
       <c r="C96">
-        <v>-208.4313519515805</v>
+        <v>-212.0683981157966</v>
       </c>
       <c r="D96">
-        <v>59.47264804841954</v>
+        <v>58.95160188420339</v>
       </c>
       <c r="E96">
-        <v>106.404</v>
+        <v>109.52</v>
       </c>
       <c r="F96">
-        <v>292.9040000000001</v>
+        <v>296.02</v>
       </c>
       <c r="G96">
         <v>25</v>
@@ -9153,37 +9153,37 @@
         <v>12.35</v>
       </c>
       <c r="M96">
-        <v>69.06676320000001</v>
+        <v>69.80151600000001</v>
       </c>
       <c r="N96">
-        <v>-56.71676320000001</v>
+        <v>-57.45151600000001</v>
       </c>
       <c r="O96">
-        <v>-19.85086712</v>
+        <v>-20.1080306</v>
       </c>
       <c r="P96">
-        <v>-36.86589608000001</v>
+        <v>-37.34348540000001</v>
       </c>
       <c r="Q96">
-        <v>-31.01589608</v>
+        <v>-31.4934854</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8831258590719232</v>
+        <v>1.050591030886308</v>
       </c>
       <c r="T96">
-        <v>12.18411150002582</v>
+        <v>14.62093380003099</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06258437198632176</v>
+        <v>0.06192558912330785</v>
       </c>
       <c r="W96">
-        <v>0.2210426050856253</v>
+        <v>0.221197946084724</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1788124913894908</v>
+        <v>0.1769302546380225</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2626676003248032</v>
+        <v>0.2645676003248032</v>
       </c>
       <c r="C97">
-        <v>-212.0683981157966</v>
+        <v>-215.6963936919866</v>
       </c>
       <c r="D97">
-        <v>58.95160188420339</v>
+        <v>58.43960630801345</v>
       </c>
       <c r="E97">
-        <v>109.52</v>
+        <v>112.636</v>
       </c>
       <c r="F97">
-        <v>296.02</v>
+        <v>299.136</v>
       </c>
       <c r="G97">
         <v>25</v>
@@ -9235,37 +9235,37 @@
         <v>12.35</v>
       </c>
       <c r="M97">
-        <v>69.80151600000001</v>
+        <v>70.5362688</v>
       </c>
       <c r="N97">
-        <v>-57.45151600000001</v>
+        <v>-58.1862688</v>
       </c>
       <c r="O97">
-        <v>-20.1080306</v>
+        <v>-20.36519408</v>
       </c>
       <c r="P97">
-        <v>-37.34348540000001</v>
+        <v>-37.82107472</v>
       </c>
       <c r="Q97">
-        <v>-31.4934854</v>
+        <v>-31.97107472</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.050591030886308</v>
+        <v>1.301788788607886</v>
       </c>
       <c r="T97">
-        <v>14.62093380003099</v>
+        <v>18.27616725003875</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06192558912330785</v>
+        <v>0.0612805309032734</v>
       </c>
       <c r="W97">
-        <v>0.221197946084724</v>
+        <v>0.2213500508130082</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1769302546380225</v>
+        <v>0.1750872311522098</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2645676003248031</v>
+        <v>0.2664676003248032</v>
       </c>
       <c r="C98">
-        <v>-215.6963936919865</v>
+        <v>-219.3155724632325</v>
       </c>
       <c r="D98">
-        <v>58.43960630801347</v>
+        <v>57.93642753676754</v>
       </c>
       <c r="E98">
-        <v>112.636</v>
+        <v>115.752</v>
       </c>
       <c r="F98">
-        <v>299.136</v>
+        <v>302.252</v>
       </c>
       <c r="G98">
         <v>25</v>
@@ -9317,37 +9317,37 @@
         <v>12.35</v>
       </c>
       <c r="M98">
-        <v>70.5362688</v>
+        <v>71.27102160000001</v>
       </c>
       <c r="N98">
-        <v>-58.1862688</v>
+        <v>-58.92102160000001</v>
       </c>
       <c r="O98">
-        <v>-20.36519408</v>
+        <v>-20.62235756</v>
       </c>
       <c r="P98">
-        <v>-37.82107472</v>
+        <v>-38.29866404000001</v>
       </c>
       <c r="Q98">
-        <v>-31.97107472</v>
+        <v>-32.44866404</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.301788788607883</v>
+        <v>1.720451718143844</v>
       </c>
       <c r="T98">
-        <v>18.2761672500387</v>
+        <v>24.3682230000516</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0612805309032734</v>
+        <v>0.06064877285272419</v>
       </c>
       <c r="W98">
-        <v>0.2213500508130082</v>
+        <v>0.2214990193613277</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1750872311522098</v>
+        <v>0.1732822081506405</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2664676003248032</v>
+        <v>0.2683676003248032</v>
       </c>
       <c r="C99">
-        <v>-219.3155724632325</v>
+        <v>-222.9261602296424</v>
       </c>
       <c r="D99">
-        <v>57.93642753676754</v>
+        <v>57.4418397703576</v>
       </c>
       <c r="E99">
-        <v>115.752</v>
+        <v>118.868</v>
       </c>
       <c r="F99">
-        <v>302.252</v>
+        <v>305.368</v>
       </c>
       <c r="G99">
         <v>25</v>
@@ -9399,37 +9399,37 @@
         <v>12.35</v>
       </c>
       <c r="M99">
-        <v>71.27102160000001</v>
+        <v>72.00577440000001</v>
       </c>
       <c r="N99">
-        <v>-58.92102160000001</v>
+        <v>-59.65577440000001</v>
       </c>
       <c r="O99">
-        <v>-20.62235756</v>
+        <v>-20.87952104</v>
       </c>
       <c r="P99">
-        <v>-38.29866404000001</v>
+        <v>-38.77625336000001</v>
       </c>
       <c r="Q99">
-        <v>-32.44866404</v>
+        <v>-32.92625336</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.720451718143844</v>
+        <v>2.557777577215765</v>
       </c>
       <c r="T99">
-        <v>24.3682230000516</v>
+        <v>36.5523345000774</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06064877285272419</v>
+        <v>0.06002990782361475</v>
       </c>
       <c r="W99">
-        <v>0.2214990193613277</v>
+        <v>0.2216449477351917</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1732822081506405</v>
+        <v>0.171514022353185</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2683676003248032</v>
+        <v>0.2702676003248032</v>
       </c>
       <c r="C100">
-        <v>-222.9261602296424</v>
+        <v>-226.5283751462084</v>
       </c>
       <c r="D100">
-        <v>57.4418397703576</v>
+        <v>56.95562485379167</v>
       </c>
       <c r="E100">
-        <v>118.868</v>
+        <v>121.984</v>
       </c>
       <c r="F100">
-        <v>305.368</v>
+        <v>308.484</v>
       </c>
       <c r="G100">
         <v>25</v>
@@ -9481,37 +9481,37 @@
         <v>12.35</v>
       </c>
       <c r="M100">
-        <v>72.00577440000001</v>
+        <v>72.74052720000002</v>
       </c>
       <c r="N100">
-        <v>-59.65577440000001</v>
+        <v>-60.39052720000002</v>
       </c>
       <c r="O100">
-        <v>-20.87952104</v>
+        <v>-21.13668452</v>
       </c>
       <c r="P100">
-        <v>-38.77625336000001</v>
+        <v>-39.25384268000001</v>
       </c>
       <c r="Q100">
-        <v>-32.92625336</v>
+        <v>-33.40384268000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.557777577215765</v>
+        <v>5.06975515443153</v>
       </c>
       <c r="T100">
-        <v>36.5523345000774</v>
+        <v>73.1046690001548</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06002990782361475</v>
+        <v>0.0594235451183257</v>
       </c>
       <c r="W100">
-        <v>0.2216449477351917</v>
+        <v>0.2217879280610988</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.171514022353185</v>
+        <v>0.1697815574809306</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2702676003248032</v>
-      </c>
-      <c r="C101">
-        <v>-226.5283751462084</v>
-      </c>
-      <c r="D101">
-        <v>56.95562485379167</v>
-      </c>
-      <c r="E101">
-        <v>121.984</v>
-      </c>
-      <c r="F101">
-        <v>308.484</v>
-      </c>
-      <c r="G101">
-        <v>25</v>
-      </c>
-      <c r="H101">
-        <v>125.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.2</v>
-      </c>
-      <c r="K101">
-        <v>5.85</v>
-      </c>
-      <c r="L101">
-        <v>12.35</v>
-      </c>
-      <c r="M101">
-        <v>72.74052720000002</v>
-      </c>
-      <c r="N101">
-        <v>-60.39052720000002</v>
-      </c>
-      <c r="O101">
-        <v>-21.13668452</v>
-      </c>
-      <c r="P101">
-        <v>-39.25384268000001</v>
-      </c>
-      <c r="Q101">
-        <v>-33.40384268000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.06975515443153</v>
-      </c>
-      <c r="T101">
-        <v>73.1046690001548</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0594235451183257</v>
-      </c>
-      <c r="W101">
-        <v>0.2217879280610988</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1697815574809306</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
